--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="145">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -1371,6 +1371,1168 @@
   </si>
   <si>
     <t xml:space="preserve">周五06:35晨间定时执行成功(克隆仓库版)；方向押跌+档位押中:破位惯性+鹰派主线+CPI落地兑现,事件降档规则原始大→中(非追结果式上修,基于当日信号独立判断:20日均幅1.04%+近5日实际档位3大2中+破位首日)；规则冻结期沿用既有规则；9/10方向√档位×后累计方向8/14、档位4/14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14 06:47</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">震荡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">锯齿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伴长短期背离</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+5.67%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期趋势涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-4.00%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期回调</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">假破位反弹受阻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">冲高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4373.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回落收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4349.7,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晨软开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4337</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重回百日线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4346</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">会前鹰派压制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(CPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息几乎确定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">噤声期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后冲高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4373.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回落约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元上影</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反弹动能未确认</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晨亚市软开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.28%[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs $4300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">两日双守假破位买盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行购金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">吨三年最大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超卖修复弹性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:47</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；方向押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位押中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">会前鹰派压制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">决议北京周四</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">02:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不在今日窗口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不触发事件降档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五冲高回落</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晨软开；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">55% vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实际</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.69%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位√</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后基于当日信号独立判断</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非追结果式；规则冻结期沿用既有规则；累计方向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、档位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5/15</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -2075,7 +3237,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2137,6 +3299,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3251,14 +4417,30 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="A17" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>4337.2</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I17" s="9"/>
       <c r="J17" s="11" t="str">
         <f aca="false">IF(OR(I17="",C17=""),"",(I17-C17)/C17)</f>
@@ -3280,9 +4462,18 @@
         <f aca="false">IF(OR(E17="",L17=""),"",IF(E17=L17,"√","×"))</f>
         <v/>
       </c>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
+      <c r="O17" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q17" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="R17" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4"/>
@@ -16364,99 +17555,99 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>96</v>
+      <c r="A1" s="17" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="18" t="n">
+      <c r="A3" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
         <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" s="18" t="n">
+      <c r="A4" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="20" t="n">
+      <c r="A5" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
         <v>0.533333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="21" t="n">
+      <c r="A6" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
         <v>0.333333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="20" t="n">
+      <c r="A7" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.533333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="21" t="n">
+      <c r="A8" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.333333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="18" t="n">
+      <c r="A9" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.583333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="18" t="str">
+      <c r="A10" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>105</v>
+      <c r="A12" s="23" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
@@ -16465,10 +17656,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -16495,88 +17686,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="23" t="s">
-        <v>110</v>
+      <c r="A1" s="24" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>112</v>
+      <c r="A3" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>114</v>
+      <c r="A4" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>116</v>
+      <c r="A5" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>118</v>
+      <c r="A6" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>120</v>
+      <c r="A7" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>121</v>
+      <c r="B8" s="26" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>122</v>
+      <c r="B9" s="26" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>124</v>
+      <c r="A10" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>126</v>
+      <c r="A11" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>128</v>
+      <c r="A12" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16584,47 +17775,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -1376,294 +1376,10 @@
     <t xml:space="preserve">2026-09-14</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-14 06:47</t>
+    <t xml:space="preserve">2026-09-14 06:40</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">震荡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">锯齿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">伴长短期背离</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+5.67%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期趋势涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-4.00%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期回调</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">假破位反弹受阻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">冲高</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4373.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回落收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4349.7,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">今晨软开</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4337</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重回百日线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4346</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下方</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">震荡(20日+0.3%锯齿)伴长短期背离(60日+5.67%长期趋势涨vs10日-4.00%短期回调)+周五4300假破位反弹受阻(冲高4373.7回落收4349.7,今晨软开4337重回百日线4346下方)</t>
   </si>
   <si>
     <r>
@@ -2115,424 +1831,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:47</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；方向押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">档位押中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:FOMC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">会前鹰派压制</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">决议北京周四</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不在今日窗口</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不触发事件降档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五冲高回落</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">今晨软开；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">55% vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">实际</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.69%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">方向</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">档位√</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后基于当日信号独立判断</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非追结果式；规则冻结期沿用既有规则；累计方向</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8/15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、档位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5/15</t>
-    </r>
+    <t xml:space="preserve">周一06:40晨间定时执行成功(克隆仓库版)；方向押跌+档位押中:FOMC会前鹰派压制(决议北京周四02:00不在今日窗口,不触发事件降档)+周五冲高回落+今晨软开；9/11结算(押跌/中55% vs 实际+0.69%涨/中:方向×档位√)后基于当日信号独立判断,非追结果式；规则冻结期沿用既有规则；累计方向8/15、档位5/15</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -3237,7 +2536,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3299,10 +2598,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4426,19 +3721,19 @@
       <c r="C17" s="9" t="n">
         <v>4337.2</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="10" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="9"/>
@@ -4462,16 +3757,16 @@
         <f aca="false">IF(OR(E17="",L17=""),"",IF(E17=L17,"√","×"))</f>
         <v/>
       </c>
-      <c r="O17" s="16" t="s">
+      <c r="O17" s="10" t="s">
         <v>98</v>
       </c>
       <c r="P17" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="Q17" s="16" t="s">
+      <c r="Q17" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="R17" s="0" t="n">
+      <c r="R17" s="1" t="n">
         <v>55</v>
       </c>
     </row>
@@ -17555,84 +16850,84 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="19" t="n">
+      <c r="B3" s="18" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
         <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="18" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
         <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="20" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
         <v>0.533333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
         <v>0.333333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="20" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.533333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.333333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="18" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.583333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="19" t="str">
+      <c r="B10" s="18" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="22" t="s">
         <v>110</v>
       </c>
     </row>
@@ -17686,87 +16981,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="26" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="26" t="s">
         <v>133</v>
       </c>
     </row>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="150">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -1832,6 +1832,1167 @@
   </si>
   <si>
     <t xml:space="preserve">周一06:40晨间定时执行成功(克隆仓库版)；方向押跌+档位押中:FOMC会前鹰派压制(决议北京周四02:00不在今日窗口,不触发事件降档)+周五冲高回落+今晨软开；9/11结算(押跌/中55% vs 实际+0.69%涨/中:方向×档位√)后基于当日信号独立判断,非追结果式；规则冻结期沿用既有规则；累计方向8/15、档位5/15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15 06:40</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">震荡</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">锯齿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伴破位后低位拉锯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周一失守</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4300/200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4313</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4296.7,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日内低</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4285.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">获承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+5.67%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期趋势涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期下行加速</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长短期背离深化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个交易日涨跌严格交替</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+$4285-4300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">两日双守获承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">噤声期今日无新鹰派催化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">决议</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">北京周四</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">02:00)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在窗外→会前空头获利回补</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+PBOC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20t)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逢低接货</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周一确认技术破位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">失守</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4300/200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4313,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五假破位反弹全数回吐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+CPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后加息押注高企但口径分歧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(30%-76%)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+CFTC/ETF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投机持仓撤离</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押超卖低位修复反弹</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周二</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；方向押涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位押中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:9/14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中双√</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实际</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.93%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后基于当日信号独立转向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非追结果式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">价格由阻力区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4337</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">移至两日双守支撑区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4296.7,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗口内噤声期无催化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">决议移出窗外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连交替</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超卖修复弹性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">决议北京周四</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">02:00</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不在窗口内不触发事件降档；规则冻结期沿用既有规则；累计方向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/16(56.3%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、档位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6/16(37.5%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；校准样本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16/20</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -2536,7 +3697,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2598,6 +3759,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3736,26 +4901,28 @@
       <c r="H17" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="11" t="str">
+      <c r="I17" s="9" t="n">
+        <v>4296.7</v>
+      </c>
+      <c r="J17" s="11" t="n">
         <f aca="false">IF(OR(I17="",C17=""),"",(I17-C17)/C17)</f>
-        <v/>
+        <v>-0.00933782163607858</v>
       </c>
       <c r="K17" s="8" t="str">
         <f aca="false">IF(J17="","",IF(J17&gt;0,"涨",IF(J17&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L17" s="8" t="str">
         <f aca="false">IF(J17="","",IF(ABS(J17)&lt;=0.003,"小",IF(ABS(J17)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M17" s="8" t="str">
         <f aca="false">IF(OR(D17="",K17=""),"",IF(D17=K17,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N17" s="8" t="str">
         <f aca="false">IF(OR(E17="",L17=""),"",IF(E17=L17,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="O17" s="10" t="s">
         <v>98</v>
@@ -3771,14 +4938,30 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="A18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4296.7</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I18" s="5"/>
       <c r="J18" s="7" t="str">
         <f aca="false">IF(OR(I18="",C18=""),"",(I18-C18)/C18)</f>
@@ -3800,9 +4983,18 @@
         <f aca="false">IF(OR(E18="",L18=""),"",IF(E18=L18,"√","×"))</f>
         <v/>
       </c>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
+      <c r="O18" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="R18" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8"/>
@@ -16850,111 +18042,111 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>101</v>
+      <c r="A1" s="17" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="18" t="n">
+      <c r="A3" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="18" t="n">
+      <c r="A4" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="20" t="n">
+      <c r="A5" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.533333333333333</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="21" t="n">
+      <c r="A6" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.333333333333333</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="20" t="n">
+      <c r="A7" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.533333333333333</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="21" t="n">
+      <c r="A8" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.333333333333333</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="18" t="n">
+      <c r="A9" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.583333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="18" t="str">
+      <c r="A10" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>110</v>
+      <c r="A12" s="23" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -16981,88 +18173,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="23" t="s">
-        <v>115</v>
+      <c r="A1" s="24" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>117</v>
+      <c r="A3" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>119</v>
+      <c r="A4" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>121</v>
+      <c r="A5" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>123</v>
+      <c r="A6" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>125</v>
+      <c r="A7" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>126</v>
+      <c r="B8" s="26" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>127</v>
+      <c r="B9" s="26" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>129</v>
+      <c r="A10" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>130</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>131</v>
+      <c r="A11" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>133</v>
+      <c r="A12" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17070,47 +18262,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="155">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -1840,1159 +1840,28 @@
     <t xml:space="preserve">2026-09-15 06:40</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">震荡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">锯齿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">伴破位后低位拉锯</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周一失守</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4300/200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4313</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4296.7,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日内低</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4285.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">获承接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+5.67%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期趋势涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日约</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期下行加速</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长短期背离深化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+    <t xml:space="preserve">震荡(20日+0.3%锯齿)伴破位后低位拉锯(周一失守$4300/200日线$4313收$4296.7,日内低$4285.9获承接;60日+5.67%长期趋势涨vs10日约-4%短期下行加速,长短期背离深化)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">近</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个交易日涨跌严格交替</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+$4285-4300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">两日双守获承接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">噤声期今日无新鹰派催化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">决议</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">北京周四</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02:00)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">在窗外→会前空头获利回补</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+PBOC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20t)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">逢低接货</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周一确认技术破位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">失守</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4300/200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4313,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五假破位反弹全数回吐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+CPI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后加息押注高企但口径分歧</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(30%-76%)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+CFTC/ETF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投机持仓撤离</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押超卖低位修复反弹</t>
-    </r>
+    <t xml:space="preserve">近5个交易日涨跌严格交替+$4285-4300两日双守获承接[未释放]+噤声期今日无新鹰派催化+决议(北京周四02:00)在窗外→会前空头获利回补[未释放]+PBOC连买21月(7月+20t)逢低接货[未释放] vs 周一确认技术破位(失守$4300/200日线$4313,周五假破位反弹全数回吐)[部分定价]+CPI后加息押注高企但口径分歧(30%-76%)[部分定价]+CFTC/ETF投机持仓撤离[部分定价]→押超卖低位修复反弹</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周二</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；方向押涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">档位押中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:9/14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中双√</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">实际</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.93%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后基于当日信号独立转向</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非追结果式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">价格由阻力区</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4337</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">移至两日双守支撑区</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4296.7,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗口内噤声期无催化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">决议移出窗外</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连交替</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超卖修复弹性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FOMC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">决议北京周四</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">02:00</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不在窗口内不触发事件降档；规则冻结期沿用既有规则；累计方向</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/16(56.3%)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、档位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6/16(37.5%)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；校准样本</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16/20</t>
-    </r>
+    <t xml:space="preserve">周二06:40晨间定时执行成功(克隆仓库版)；方向押涨+档位押中:9/14押跌/中双√(实际-0.93%跌/中)后基于当日信号独立转向(非追结果式:价格由阻力区4337移至两日双守支撑区4296.7,窗口内噤声期无催化+决议移出窗外+5连交替+超卖修复弹性)；FOMC决议北京周四02:00不在窗口内不触发事件降档；规则冻结期沿用既有规则；累计方向9/16(56.3%)、档位6/16(37.5%)；校准样本16/20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16 06:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">趋势跌(20日-2.82%·LBMA9/14单日-2.72%砸穿箱体)·10日动能-6.48%加速下行;60日仅+1.67%长期动能钝化vs短期趋势跌,短期主导;FOMC决议(北京周四02:00)落入窗口内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20日市况由震荡翻趋势跌+10日动能-6.48%[未释放]+FOMC决议(北京周四02:00)移入窗口:8月CPI/PPI偏热+收益率上行+能源涨价强化加息押注(30%-76%)[部分定价]+破位未修复(100日均线下方,200日线$4,313转压,9/15仅+0.07%弱修复)[部分定价]+锯齿交替昨日涨今日轮跌[未释放] vs PBOC连买21月(7月+20t)+$4,285-4,300三日承接[未释放]+决议若按兵不动空头回补弹性[未释放]→押趋势市空头延续至决议落地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周三06:50晨间定时执行成功(克隆仓库版)；9/15结算√方向×档位(押涨/中,实际+0.07%涨/小)后转押跌:非追结果式——客观变化=20日市况由震荡(+0.3%)翻转趋势跌(-2.82%)+FOMC决议移入窗口(北京周四02:00)+破位后修复乏力(+0.07%)；事件降档不适用(按9/15口径:事件簇期间会前收敛两次失效,9/10押小实得-1.90%大档,决议反应期在窗内本身即波动源)；规则冻结期沿用既有规则；累计方向10/17(58.8%)、档位6/17(35.3%)；校准样本17/20</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -3697,7 +2566,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3759,10 +2628,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4947,88 +3812,115 @@
       <c r="C18" s="5" t="n">
         <v>4296.7</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="7" t="str">
+      <c r="I18" s="5" t="n">
+        <v>4299.8</v>
+      </c>
+      <c r="J18" s="7" t="n">
         <f aca="false">IF(OR(I18="",C18=""),"",(I18-C18)/C18)</f>
-        <v/>
+        <v>0.000721483929527396</v>
       </c>
       <c r="K18" s="4" t="str">
         <f aca="false">IF(J18="","",IF(J18&gt;0,"涨",IF(J18&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L18" s="4" t="str">
         <f aca="false">IF(J18="","",IF(ABS(J18)&lt;=0.003,"小",IF(ABS(J18)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>小</v>
       </c>
       <c r="M18" s="4" t="str">
         <f aca="false">IF(OR(D18="",K18=""),"",IF(D18=K18,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N18" s="4" t="str">
         <f aca="false">IF(OR(E18="",L18=""),"",IF(E18=L18,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O18" s="16" t="s">
+        <v>×</v>
+      </c>
+      <c r="O18" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="P18" s="16" t="s">
+      <c r="P18" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="Q18" s="16" t="s">
+      <c r="Q18" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="R18" s="0" t="n">
+      <c r="R18" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="11" t="str">
+      <c r="A19" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>4298.7</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="7" t="str">
         <f aca="false">IF(OR(I19="",C19=""),"",(I19-C19)/C19)</f>
         <v/>
       </c>
-      <c r="K19" s="8" t="str">
+      <c r="K19" s="4" t="str">
         <f aca="false">IF(J19="","",IF(J19&gt;0,"涨",IF(J19&lt;0,"跌","平")))</f>
         <v/>
       </c>
-      <c r="L19" s="8" t="str">
+      <c r="L19" s="4" t="str">
         <f aca="false">IF(J19="","",IF(ABS(J19)&lt;=0.003,"小",IF(ABS(J19)&lt;=0.01,"中","大")))</f>
         <v/>
       </c>
-      <c r="M19" s="8" t="str">
+      <c r="M19" s="4" t="str">
         <f aca="false">IF(OR(D19="",K19=""),"",IF(D19=K19,"√","×"))</f>
         <v/>
       </c>
-      <c r="N19" s="8" t="str">
+      <c r="N19" s="4" t="str">
         <f aca="false">IF(OR(E19="",L19=""),"",IF(E19=L19,"√","×"))</f>
         <v/>
       </c>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
+      <c r="O19" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4"/>
@@ -18042,111 +16934,111 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
-        <v>106</v>
+      <c r="A1" s="16" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B3" s="19" t="n">
+      <c r="A3" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" s="18" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>108</v>
-      </c>
-      <c r="B4" s="19" t="n">
+      <c r="A4" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="18" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" s="21" t="n">
+      <c r="A5" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="20" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.5625</v>
+        <v>0.588235294117647</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="22" t="n">
+      <c r="A6" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.375</v>
+        <v>0.352941176470588</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="21" t="n">
+      <c r="A7" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="20" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.5625</v>
+        <v>0.588235294117647</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="22" t="n">
+      <c r="A8" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.375</v>
+        <v>0.352941176470588</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="19" t="n">
+      <c r="A9" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="18" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.583333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" s="19" t="str">
+      <c r="A10" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" s="18" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
-        <v>115</v>
+      <c r="A12" s="22" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -18173,88 +17065,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>120</v>
+      <c r="A1" s="23" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>122</v>
+      <c r="A3" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>124</v>
+      <c r="A4" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
-        <v>125</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>126</v>
+      <c r="A5" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>128</v>
+      <c r="A6" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>130</v>
+      <c r="A7" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>131</v>
+      <c r="B8" s="25" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>132</v>
+      <c r="B9" s="25" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>134</v>
+      <c r="A10" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>136</v>
+      <c r="A11" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>138</v>
+      <c r="A12" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18262,47 +17154,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -1885,129 +1885,7 @@
     <t xml:space="preserve">2026-09-18 06:37</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">震荡</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-1.71%)·60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+7.55%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期趋势涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-1.23%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期修复背离收敛</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·FOMC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">落地次日逆势大涨后的延续消化日</t>
-    </r>
+    <t xml:space="preserve">震荡(20日-1.71%)·60日+7.55%长期趋势涨vs10日-1.23%短期修复背离收敛·FOMC落地次日逆势大涨后的延续消化日</t>
   </si>
   <si>
     <r>
@@ -2411,158 +2289,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:31</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">定时执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；凌晨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">00:22 Actions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">提前结算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/17</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行已按口径修正</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中段价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4367.8→4346.90)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">并</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">recalc</t>
-    </r>
+    <t xml:space="preserve">周五06:31定时执行成功(克隆仓库版)；凌晨00:22 Actions提前结算9/17行已按口径修正(中段价4367.8→4346.90)并recalc</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -3267,7 +2994,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3329,10 +3056,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4700,52 +4423,54 @@
       <c r="C21" s="9" t="n">
         <v>4347.8</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H21" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="11" t="str">
+      <c r="I21" s="9" t="n">
+        <v>4379</v>
+      </c>
+      <c r="J21" s="11" t="n">
         <f aca="false">IF(OR(I21="",C21=""),"",(I21-C21)/C21)</f>
-        <v/>
+        <v>0.0071760430562583</v>
       </c>
       <c r="K21" s="8" t="str">
         <f aca="false">IF(J21="","",IF(J21&gt;0,"涨",IF(J21&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L21" s="8" t="str">
         <f aca="false">IF(J21="","",IF(ABS(J21)&lt;=0.003,"小",IF(ABS(J21)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M21" s="8" t="str">
         <f aca="false">IF(OR(D21="",K21=""),"",IF(D21=K21,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N21" s="8" t="str">
         <f aca="false">IF(OR(E21="",L21=""),"",IF(E21=L21,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O21" s="16" t="s">
+        <v>√</v>
+      </c>
+      <c r="O21" s="10" t="s">
         <v>118</v>
       </c>
       <c r="P21" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="Q21" s="16" t="s">
+      <c r="Q21" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="R21" s="0" t="n">
+      <c r="R21" s="1" t="n">
         <v>55</v>
       </c>
     </row>
@@ -17693,84 +17418,84 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="19" t="n">
+      <c r="B3" s="18" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="18" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
         <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="20" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.578947368421053</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.368421052631579</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="20" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.578947368421053</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.368421052631579</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="18" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.571428571428571</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="B10" s="19" t="str">
+      <c r="B10" s="18" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="22" t="s">
         <v>130</v>
       </c>
     </row>
@@ -17789,7 +17514,7 @@
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17824,87 +17549,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="26" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="26" t="s">
         <v>153</v>
       </c>
     </row>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="170">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -2290,6 +2290,777 @@
   </si>
   <si>
     <t xml:space="preserve">周五06:31定时执行成功(克隆仓库版)；凌晨00:22 Actions提前结算9/17行已按口径修正(中段价4367.8→4346.90)并recalc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-21 06:53</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-3.01%·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗口滚动由震荡翻空</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+6.78%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1.52%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期修复背离</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派落地后第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交易日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五午后冲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,396.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">遭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,380-4,400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阻力带打回收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,379+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周一平开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,377.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无追涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+VIX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三连降至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险退潮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日窗口滚动翻趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-3.01%+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点阵图</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16/18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年内再加息余波</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行连购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月与地缘尾部垫底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:53</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；方向押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位押中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阻力带供给周五实测确认</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平开无追涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险退潮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">市况翻趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">两连涨窗口后回吐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">校准达标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20/20(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">校准良好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+4.0pp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏保守</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,Brier 0.2440),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">冻结期已满</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三条待改项待用户定夺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本判断沿用冻结前规则</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -2994,7 +3765,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3056,6 +3827,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4475,14 +5250,30 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="A22" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>4377.5</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I22" s="5"/>
       <c r="J22" s="7" t="str">
         <f aca="false">IF(OR(I22="",C22=""),"",(I22-C22)/C22)</f>
@@ -4504,9 +5295,18 @@
         <f aca="false">IF(OR(E22="",L22=""),"",IF(E22=L22,"√","×"))</f>
         <v/>
       </c>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
+      <c r="O22" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q22" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="R22" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8"/>
@@ -17418,99 +18218,99 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>121</v>
+      <c r="A1" s="17" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="18" t="n">
+      <c r="A3" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" s="18" t="n">
+      <c r="A4" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="B5" s="20" t="n">
+      <c r="A5" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
         <v>0.6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="B6" s="21" t="n">
+      <c r="A6" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
         <v>0.4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="20" t="n">
+      <c r="A7" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="21" t="n">
+      <c r="A8" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" s="18" t="n">
+      <c r="A9" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.571428571428571</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="18" t="str">
+      <c r="A10" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>130</v>
+      <c r="A12" s="23" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
@@ -17519,10 +18319,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -17549,88 +18349,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="23" t="s">
-        <v>135</v>
+      <c r="A1" s="24" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>137</v>
+      <c r="A3" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>139</v>
+      <c r="A4" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>141</v>
+      <c r="A5" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>143</v>
+      <c r="A6" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>145</v>
+      <c r="A7" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>146</v>
+      <c r="B8" s="26" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>147</v>
+      <c r="B9" s="26" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>149</v>
+      <c r="A10" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>151</v>
+      <c r="A11" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>153</v>
+      <c r="A12" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17638,47 +18438,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="175">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -2298,475 +2298,21 @@
     <t xml:space="preserve">2026-09-21 06:53</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-3.01%·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗口滚动由震荡翻空</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+6.78%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-1.52%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期修复背离</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·FOMC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派落地后第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">交易日</t>
-    </r>
+    <t xml:space="preserve">趋势跌(20日-3.01%·窗口滚动由震荡翻空)·60日+6.78%长期涨vs10日-1.52%短期修复背离·FOMC鹰派落地后第3交易日</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五午后冲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,396.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">遭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,380-4,400</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">阻力带打回收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,379+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周一平开</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,377.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">无追涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+VIX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三连降至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14.81</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">避险退潮</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日窗口滚动翻趋势跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-3.01%+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点阵图</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16/18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年内再加息余波</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">央行连购</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个月与地缘尾部垫底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
+    <t xml:space="preserve">周五午后冲$4,396.9遭$4,380-4,400阻力带打回收$4,379+周一平开$4,377.5无追涨[未释放]+VIX三连降至14.81避险退潮[部分定价]+20日窗口滚动翻趋势跌-3.01%+点阵图16/18年内再加息余波[已定价] vs 央行连购22个月与地缘尾部垫底[未释放]</t>
   </si>
   <si>
+    <t xml:space="preserve">周一06:53晨间定时执行成功(克隆仓库版)；方向押跌+档位押中:阻力带供给周五实测确认+平开无追涨+避险退潮+市况翻趋势跌,两连涨窗口后回吐;校准达标20/20(校准良好+4.0pp偏保守,Brier 0.2440),冻结期已满,三条待改项待用户定夺,本判断沿用冻结前规则</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22 06:35</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2774,7 +2320,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">周一</t>
+      <t xml:space="preserve">趋势跌</t>
     </r>
     <r>
       <rPr>
@@ -2784,7 +2330,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">06:53</t>
+      <t xml:space="preserve">(20</t>
     </r>
     <r>
       <rPr>
@@ -2793,6 +2339,532 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-3.01%)·60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+6.78%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期反弹回吐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1/3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">背离</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派落地后第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交易日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,353.9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">贴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,348</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">定盘支撑边缘惯性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">通胀热数据强化年内再加息预期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元一个月高位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·10Y~4.96%[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+CFTC/ETF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投机持仓双降</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+VIX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三连降</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.81</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险退潮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行连购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中国</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20.2t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、波兰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2+51t)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,348</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技术承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周二</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">晨间定时执行成功</t>
     </r>
     <r>
@@ -2822,7 +2894,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">);</t>
     </r>
     <r>
       <rPr>
@@ -2831,7 +2903,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">；方向押跌</t>
+      <t xml:space="preserve">方向押跌</t>
     </r>
     <r>
       <rPr>
@@ -2869,7 +2941,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">阻力带供给周五实测确认</t>
+      <t xml:space="preserve">支撑边缘惯性</t>
     </r>
     <r>
       <rPr>
@@ -2888,7 +2960,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">平开无追涨</t>
+      <t xml:space="preserve">加息预期边际强化</t>
     </r>
     <r>
       <rPr>
@@ -2907,7 +2979,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">避险退潮</t>
+      <t xml:space="preserve">投机离场</t>
     </r>
     <r>
       <rPr>
@@ -2926,7 +2998,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">市况翻趋势跌</t>
+      <t xml:space="preserve">卖压叙事主导</t>
     </r>
     <r>
       <rPr>
@@ -2945,7 +3017,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">两连涨窗口后回吐</t>
+      <t xml:space="preserve">两连√后不机械连押亦不因连对加码</t>
     </r>
     <r>
       <rPr>
@@ -2964,7 +3036,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">校准达标</t>
+      <t xml:space="preserve">校准</t>
     </r>
     <r>
       <rPr>
@@ -2974,7 +3046,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20/20(</t>
+      <t xml:space="preserve">21/20</t>
     </r>
     <r>
       <rPr>
@@ -2983,7 +3055,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">校准良好</t>
+      <t xml:space="preserve">达标偏保守</t>
     </r>
     <r>
       <rPr>
@@ -2993,26 +3065,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+4.0pp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏保守</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,Brier 0.2440),</t>
+      <t xml:space="preserve">+6.0pp(Brier 0.2420),</t>
     </r>
     <r>
       <rPr>
@@ -3830,7 +3883,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5259,64 +5312,82 @@
       <c r="C22" s="5" t="n">
         <v>4377.5</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I22" s="5"/>
-      <c r="J22" s="7" t="str">
+      <c r="I22" s="5" t="n">
+        <v>4353.9</v>
+      </c>
+      <c r="J22" s="7" t="n">
         <f aca="false">IF(OR(I22="",C22=""),"",(I22-C22)/C22)</f>
-        <v/>
+        <v>-0.00539120502569968</v>
       </c>
       <c r="K22" s="4" t="str">
         <f aca="false">IF(J22="","",IF(J22&gt;0,"涨",IF(J22&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L22" s="4" t="str">
         <f aca="false">IF(J22="","",IF(ABS(J22)&lt;=0.003,"小",IF(ABS(J22)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M22" s="4" t="str">
         <f aca="false">IF(OR(D22="",K22=""),"",IF(D22=K22,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N22" s="4" t="str">
         <f aca="false">IF(OR(E22="",L22=""),"",IF(E22=L22,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O22" s="16" t="s">
+        <v>√</v>
+      </c>
+      <c r="O22" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="P22" s="16" t="s">
+      <c r="P22" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="Q22" s="16" t="s">
+      <c r="Q22" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="R22" s="0" t="n">
+      <c r="R22" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
+      <c r="A23" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>4353.9</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I23" s="9"/>
       <c r="J23" s="11" t="str">
         <f aca="false">IF(OR(I23="",C23=""),"",(I23-C23)/C23)</f>
@@ -5338,9 +5409,18 @@
         <f aca="false">IF(OR(E23="",L23=""),"",IF(E23=L23,"√","×"))</f>
         <v/>
       </c>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="8"/>
+      <c r="O23" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="P23" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q23" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="R23" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
@@ -18219,75 +18299,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.6</v>
+        <v>0.619047619047619</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.4</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.6</v>
+        <v>0.619047619047619</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.4</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.571428571428571</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -18296,33 +18376,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -18350,47 +18430,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18398,7 +18478,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18406,31 +18486,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18438,47 +18518,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="180">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -2313,550 +2313,840 @@
     <t xml:space="preserve">2026-09-22 06:35</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-3.01%)·60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+6.78%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期反弹回吐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1/3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">背离</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·FOMC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派落地后第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">交易日</t>
-    </r>
+    <t xml:space="preserve">趋势跌(20日-3.01%)·60日+6.78%长期涨vs短期反弹回吐1/3背离·FOMC鹰派落地后第4交易日</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,353.9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">贴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,348</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">定盘支撑边缘惯性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通胀热数据强化年内再加息预期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元一个月高位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·10Y~4.96%[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+CFTC/ETF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投机持仓双降</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+VIX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三连降</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14.81</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">避险退潮</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">央行连购</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中国</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20.2t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、波兰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Q2+51t)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,348</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">技术承接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
+    <t xml:space="preserve">昨收$4,353.9贴$4,348定盘支撑边缘惯性[部分定价]+通胀热数据强化年内再加息预期·美元一个月高位·10Y~4.96%[已定价]+CFTC/ETF投机持仓双降[未释放]+VIX三连降14.81避险退潮[部分定价] vs 央行连购22个月(中国8月+20.2t、波兰Q2+51t)与$4,348技术承接[未释放]</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周二</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:35</t>
+    <t xml:space="preserve">周二06:35晨间定时执行成功(克隆仓库版);方向押跌+档位押中:支撑边缘惯性+加息预期边际强化+投机离场+卖压叙事主导,两连√后不机械连押亦不因连对加码;校准21/20达标偏保守+6.0pp(Brier 0.2420),冻结期已满,三条待改项待用户定夺,本判断沿用冻结前规则</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23 06:40</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-5.63%·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗口滚动纳入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8/21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高基数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+7.40%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1.78%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期整理背离</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派落地后第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交易日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隔夜深</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回补次日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隔夜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">型吸收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下探</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,314.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">创两周新低却以</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,364.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">更高收盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.25%,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连续两窗美盘强势回补</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行连购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20t,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">波兰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2+51t)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,310-4,334</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派钝化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加息落地</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点阵图已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收益率企稳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs $4,380-4,400</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阻力带两度实测有效</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+CFTC/ETF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投机持仓续降</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+VIX14.87</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险退潮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今窗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Fedspeak/PMI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏鹰风险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押区间承托的小幅续涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上沿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,378</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">为分水岭</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周三</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:40</t>
     </r>
     <r>
       <rPr>
@@ -2894,16 +3184,244 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">方向押跌</t>
+      <t xml:space="preserve">);9/22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">××(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实际</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.25%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.91%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在轨被美盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">型回补逆转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后方向转涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非追结果——独立新证据</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">更低下探</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,314.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">却更高收盘的卖压吸收形态</t>
     </r>
     <r>
       <rPr>
@@ -2922,7 +3440,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">档位押中</t>
+      <t xml:space="preserve">美元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收益率由续升转企稳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">幅度押小</t>
     </r>
     <r>
       <rPr>
@@ -2941,64 +3497,102 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">支撑边缘惯性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加息预期边际强化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投机离场</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">卖压叙事主导</t>
+      <t xml:space="preserve">动能衰减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">|-0.54%|→|+0.25%|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">递减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">事件真空</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已落地</t>
     </r>
     <r>
       <rPr>
@@ -3017,7 +3611,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">两连√后不机械连押亦不因连对加码</t>
+      <t xml:space="preserve">耐用品周五</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/PCE9/30)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双向关键位距现价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt;0.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区间收敛</t>
     </r>
     <r>
       <rPr>
@@ -3046,26 +3678,64 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">21/20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">达标偏保守</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+6.0pp(Brier 0.2420),</t>
+      <t xml:space="preserve">22/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">达标校准良好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(+3.2pp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">±5pp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">容忍带</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,Brier0.2448),</t>
     </r>
     <r>
       <rPr>
@@ -3883,7 +4553,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5373,64 +6043,82 @@
       <c r="C23" s="9" t="n">
         <v>4353.9</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="11" t="str">
+      <c r="I23" s="9" t="n">
+        <v>4364.7</v>
+      </c>
+      <c r="J23" s="11" t="n">
         <f aca="false">IF(OR(I23="",C23=""),"",(I23-C23)/C23)</f>
-        <v/>
+        <v>0.00248053469303387</v>
       </c>
       <c r="K23" s="8" t="str">
         <f aca="false">IF(J23="","",IF(J23&gt;0,"涨",IF(J23&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L23" s="8" t="str">
         <f aca="false">IF(J23="","",IF(ABS(J23)&lt;=0.003,"小",IF(ABS(J23)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>小</v>
       </c>
       <c r="M23" s="8" t="str">
         <f aca="false">IF(OR(D23="",K23=""),"",IF(D23=K23,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N23" s="8" t="str">
         <f aca="false">IF(OR(E23="",L23=""),"",IF(E23=L23,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O23" s="16" t="s">
+        <v>×</v>
+      </c>
+      <c r="O23" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="P23" s="16" t="s">
+      <c r="P23" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="Q23" s="16" t="s">
+      <c r="Q23" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="R23" s="0" t="n">
+      <c r="R23" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="A24" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>4364.7</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I24" s="5"/>
       <c r="J24" s="7" t="str">
         <f aca="false">IF(OR(I24="",C24=""),"",(I24-C24)/C24)</f>
@@ -5452,9 +6140,18 @@
         <f aca="false">IF(OR(E24="",L24=""),"",IF(E24=L24,"√","×"))</f>
         <v/>
       </c>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
+      <c r="O24" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="P24" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q24" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="R24" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8"/>
@@ -18299,75 +18996,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.619047619047619</v>
+        <v>0.590909090909091</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.428571428571429</v>
+        <v>0.409090909090909</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.619047619047619</v>
+        <v>0.590909090909091</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.428571428571429</v>
+        <v>0.409090909090909</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.6</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -18376,33 +19073,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -18430,47 +19127,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18478,7 +19175,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18486,31 +19183,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18518,47 +19215,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="预测日志" sheetId="1" state="visible" r:id="rId2"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="185">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -2328,825 +2328,1030 @@
     <t xml:space="preserve">2026-09-23 06:40</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-5.63%·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗口滚动纳入</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8/21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">高基数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+7.40%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-1.78%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期整理背离</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·FOMC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派落地后第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">交易日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隔夜深</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回补次日</t>
-    </r>
+    <t xml:space="preserve">趋势跌(20日-5.63%·窗口滚动纳入8/21高基数)·60日+7.40%长期涨vs10日-1.78%短期整理背离·FOMC鹰派落地后第5交易日·隔夜深V回补次日</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隔夜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">型吸收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下探</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,314.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">创两周新低却以</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,364.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">更高收盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.25%,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连续两窗美盘强势回补</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">央行连购</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20t,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">波兰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Q2+51t)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,310-4,334</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双底承接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派钝化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加息落地</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点阵图已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收益率企稳</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] vs $4,380-4,400</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">阻力带两度实测有效</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+CFTC/ETF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投机持仓续降</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+VIX14.87</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">避险退潮</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">今窗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Fedspeak/PMI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏鹰风险</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押区间承托的小幅续涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上沿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,378</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">为分水岭</t>
-    </r>
+    <t xml:space="preserve">隔夜V型吸收(下探$4,314.8创两周新低却以$4,364.7更高收盘+0.25%,连续两窗美盘强势回补)[未释放]+央行连购22个月(7月+20t,波兰Q2+51t)与$4,310-4,334双底承接[未释放]+鹰派钝化(加息落地+点阵图已定价,美元/收益率企稳)[已定价] vs $4,380-4,400阻力带两度实测有效[部分定价]+CFTC/ETF投机持仓续降+VIX14.87避险退潮[部分定价]+今窗Fedspeak/PMI偏鹰风险[未释放]→押区间承托的小幅续涨,上沿$4,378为分水岭</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周三</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:40</t>
+    <t xml:space="preserve">周三06:40晨间定时执行成功(克隆仓库版);9/22结算××(押跌/中vs实际+0.25%涨/小,午后-0.91%在轨被美盘V型回补逆转)后方向转涨:非追结果——独立新证据=更低下探$4,314.8却更高收盘的卖压吸收形态+美元/收益率由续升转企稳;幅度押小:动能衰减(近2窗|-0.54%|→|+0.25%|递减)+事件真空(FOMC已落地,耐用品周五/PCE9/30)+双向关键位距现价&lt;0.4%区间收敛;校准22/20达标校准良好(+3.2pp在±5pp容忍带,Brier0.2448),冻结期已满,三条待改项待用户定夺,本判断沿用冻结前规则</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24 06:35</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-7.16%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连续第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日加深</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+7.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LBMA-1.58%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期续弱背离</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派落地后第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交易日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨日破位大阴线次日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨日破位大阴线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1.72%(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">跌穿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,314.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底颈线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回撤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,314.66+$4,300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">整数关</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,289.60,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">场景</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兑现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日趋势跌加深至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-7.16%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">顺势</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派加息预期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点阵图</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16/18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年内再加息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+PPI/CPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">热</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元一个月高位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·10Y~4.96%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">压制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+VIX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">四连降至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险溢价归零</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+CFTC/ETF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投机持仓降至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2019</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中低位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs $4,265-4,267</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三重底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9/14 LBMA/9/18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">现货</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/9/23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">亚市</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与央行逢低承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(PBOC 21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">波兰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2+51t)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">sub-$4,300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">goodish</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反弹买盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+9/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗口涨跌严格交替</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押顺势低位阴跌收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,262-4,276,$4,265</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">为存亡线、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,314.66</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">为反压确认线</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周四</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:32</t>
     </r>
     <r>
       <rPr>
@@ -3184,7 +3389,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">);9/22</t>
+      <t xml:space="preserve">);9/23</t>
     </r>
     <r>
       <rPr>
@@ -3212,7 +3417,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">押跌</t>
+      <t xml:space="preserve">押涨</t>
     </r>
     <r>
       <rPr>
@@ -3231,7 +3436,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">中</t>
+      <t xml:space="preserve">小</t>
     </r>
     <r>
       <rPr>
@@ -3260,16 +3465,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+0.25%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">涨</t>
+      <t xml:space="preserve">-1.72%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">跌</t>
     </r>
     <r>
       <rPr>
@@ -3288,7 +3493,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">小</t>
+      <t xml:space="preserve">大</t>
     </r>
     <r>
       <rPr>
@@ -3307,45 +3512,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">午后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.91%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">在轨被美盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">型回补逆转</t>
+      <t xml:space="preserve">场景</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兑现且更深</t>
     </r>
     <r>
       <rPr>
@@ -3364,7 +3550,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">后方向转涨</t>
+      <t xml:space="preserve">后方向顺势转跌</t>
     </r>
     <r>
       <rPr>
@@ -3383,7 +3569,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">非追结果——独立新证据</t>
+      <t xml:space="preserve">非追结果——独立依据</t>
     </r>
     <r>
       <rPr>
@@ -3402,26 +3588,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">更低下探</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,314.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">却更高收盘的卖压吸收形态</t>
+      <t xml:space="preserve">破位结构</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">($4,310-4,334</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三重支撑带单日全数跌穿</t>
     </r>
     <r>
       <rPr>
@@ -3440,26 +3626,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">美元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收益率由续升转企稳</t>
+      <t xml:space="preserve">隔夜贴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,289</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低位横盘无反抽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势标签</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-7.16%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连续加深</t>
     </r>
     <r>
       <rPr>
@@ -3478,7 +3702,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">幅度押小</t>
+      <t xml:space="preserve">幅度押中</t>
     </r>
     <r>
       <rPr>
@@ -3497,102 +3721,140 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">动能衰减</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">近</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">|-0.54%|→|+0.25%|</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">递减</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">事件真空</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(FOMC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已落地</t>
+      <t xml:space="preserve">破位惯性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日日均波幅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.99%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">但</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,265</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三重底近在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.5%+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行承接封深跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">校准</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">23/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">达标校准良好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.7pp(Brier0.2473),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">冻结期已满</t>
     </r>
     <r>
       <rPr>
@@ -3611,45 +3873,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">耐用品周五</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/PCE9/30)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双向关键位距现价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">&lt;0.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">区间收敛</t>
+      <t xml:space="preserve">三条待改项待用户定夺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本判断沿用冻结前规则</t>
     </r>
     <r>
       <rPr>
@@ -3668,121 +3911,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">校准</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22/20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">达标校准良好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(+3.2pp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">±5pp</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">容忍带</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,Brier0.2448),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">冻结期已满</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三条待改项待用户定夺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本判断沿用冻结前规则</t>
+      <t xml:space="preserve">本沙盒无</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">recalc.py,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">soffice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">log.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公式</t>
     </r>
   </si>
   <si>
@@ -4553,7 +4739,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6104,64 +6290,82 @@
       <c r="C24" s="5" t="n">
         <v>4364.7</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="16" t="s">
+      <c r="H24" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="5"/>
-      <c r="J24" s="7" t="str">
+      <c r="I24" s="5" t="n">
+        <v>4289.6</v>
+      </c>
+      <c r="J24" s="7" t="n">
         <f aca="false">IF(OR(I24="",C24=""),"",(I24-C24)/C24)</f>
-        <v/>
+        <v>-0.0172062226498956</v>
       </c>
       <c r="K24" s="4" t="str">
         <f aca="false">IF(J24="","",IF(J24&gt;0,"涨",IF(J24&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L24" s="4" t="str">
         <f aca="false">IF(J24="","",IF(ABS(J24)&lt;=0.003,"小",IF(ABS(J24)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>大</v>
       </c>
       <c r="M24" s="4" t="str">
         <f aca="false">IF(OR(D24="",K24=""),"",IF(D24=K24,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N24" s="4" t="str">
         <f aca="false">IF(OR(E24="",L24=""),"",IF(E24=L24,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O24" s="16" t="s">
+        <v>×</v>
+      </c>
+      <c r="O24" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="P24" s="16" t="s">
+      <c r="P24" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="Q24" s="16" t="s">
+      <c r="Q24" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="R24" s="0" t="n">
+      <c r="R24" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
+      <c r="A25" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>4289.1</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I25" s="9"/>
       <c r="J25" s="11" t="str">
         <f aca="false">IF(OR(I25="",C25=""),"",(I25-C25)/C25)</f>
@@ -6183,9 +6387,18 @@
         <f aca="false">IF(OR(E25="",L25=""),"",IF(E25=L25,"√","×"))</f>
         <v/>
       </c>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
+      <c r="O25" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="P25" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q25" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="R25" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
@@ -18996,75 +19209,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.590909090909091</v>
+        <v>0.565217391304348</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.409090909090909</v>
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.590909090909091</v>
+        <v>0.565217391304348</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.409090909090909</v>
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.5625</v>
+        <v>0.529411764705882</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -19073,33 +19286,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -19127,47 +19340,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19175,7 +19388,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19183,31 +19396,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19215,47 +19428,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="190">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -2343,1015 +2343,1268 @@
     <t xml:space="preserve">2026-09-24 06:35</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-7.16%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连续第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日加深</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+7.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LBMA-1.58%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期续弱背离</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·FOMC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派落地后第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">交易日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨日破位大阴线次日</t>
-    </r>
+    <t xml:space="preserve">趋势跌(20日-7.16%连续第3日加深)·60日+7.4%长期涨vs10日LBMA-1.58%短期续弱背离·FOMC鹰派落地后第6交易日·昨日破位大阴线次日</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨日破位大阴线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-1.72%(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">跌穿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,314.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双底颈线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回撤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,314.66+$4,300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">整数关</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,289.60,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">场景</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兑现</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日趋势跌加深至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-7.16%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">顺势</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派加息预期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点阵图</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16/18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年内再加息</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+PPI/CPI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元一个月高位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·10Y~4.96%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">压制</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+VIX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">四连降至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14.21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">避险溢价归零</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+CFTC/ETF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投机持仓降至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2019</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年中低位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] vs $4,265-4,267</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三重底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(9/14 LBMA/9/18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">现货</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/9/23</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">亚市</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与央行逢低承接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(PBOC 21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">波兰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Q2+51t)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sub-$4,300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">现</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">goodish</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">反弹买盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+9/8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗口涨跌严格交替</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押顺势低位阴跌收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,262-4,276,$4,265</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">为存亡线、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,314.66</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">为反压确认线</t>
-    </r>
+    <t xml:space="preserve">昨日破位大阴线-1.72%(跌穿$4,314.8双底颈线+50%回撤$4,314.66+$4,300整数关,收$4,289.60,场景D兑现)[部分定价]+20日趋势跌加深至-7.16%顺势[已定价]+鹰派加息预期(点阵图16/18年内再加息+PPI/CPI热)美元一个月高位·10Y~4.96%压制[已定价]+VIX四连降至14.21避险溢价归零[部分定价]+CFTC/ETF投机持仓降至2019年中低位[未释放] vs $4,265-4,267三重底(9/14 LBMA/9/18现货/9/23亚市)与央行逢低承接(PBOC 21连月+波兰Q2+51t)[未释放]+昨日sub-$4,300现goodish反弹买盘[未释放]+9/8起8窗口涨跌严格交替[未释放]→押顺势低位阴跌收$4,262-4,276,$4,265为存亡线、$4,314.66为反压确认线</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周四</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:32</t>
+    <t xml:space="preserve">周四06:32晨间定时执行成功(克隆仓库版);9/23结算××(押涨/小vs实际-1.72%跌/大,场景D兑现且更深)后方向顺势转跌:非追结果——独立依据=破位结构($4,310-4,334三重支撑带单日全数跌穿+隔夜贴$4,289低位横盘无反抽)+趋势标签-7.16%连续加深;幅度押中:破位惯性+20日日均波幅0.99%但$4,265三重底近在-0.5%+央行承接封深跌;校准23/20达标校准良好+0.7pp(Brier0.2473),冻结期已满,三条待改项待用户定夺,本判断沿用冻结前规则;本沙盒无recalc.py,已用soffice重算log.xlsx公式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25 06:38</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-7.17%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连续第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日深位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+7.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LBMA-2.32%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期续弱背离</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派落地后第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交易日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三重底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,265-4,267</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上沿压缩待变</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(-0.15%)·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">耐用品订单</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">密歇根终值日</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-7.17%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连续深位顺势</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破位结构未修复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未收复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,300/$4,314.66</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反压</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隔夜横盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派延续</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点阵图</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16/18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年内再加息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+PPI/CPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">热</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元一个月高位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·10Y~4.96%[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+VIX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">四连降</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险溢价归零</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技术指标全线偏空</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日均线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">~$4,369</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">封盖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+MACD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">负</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+RSI 36.5-44.6)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晚耐用品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">密歇根若偏热点火</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs $4,265-4,267</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三重底第四次防守</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9/14/9/18/9/24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三守成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(PBOC 22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">创纪录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">波兰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2+51t,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逢低买入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+CCI-262</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超卖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动能衰减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(-1.72%→-0.39%→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隔夜平</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投机持仓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2019</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中低位抛压衰竭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五空头回补</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押顺势压缩后向下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,265</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">止损延伸至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,240-4,262(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三重底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行承接封深跌不押大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,$4,314.66</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">为翻多确认线</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:31</t>
     </r>
     <r>
       <rPr>
@@ -3389,35 +3642,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">);9/23</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">××(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押涨</t>
+      <t xml:space="preserve">);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/24√√(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押跌</t>
     </r>
     <r>
       <rPr>
@@ -3436,7 +3689,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">小</t>
+      <t xml:space="preserve">中</t>
     </r>
     <r>
       <rPr>
@@ -3465,7 +3718,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-1.72%</t>
+      <t xml:space="preserve">-0.39%</t>
     </r>
     <r>
       <rPr>
@@ -3493,7 +3746,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">大</t>
+      <t xml:space="preserve">中</t>
     </r>
     <r>
       <rPr>
@@ -3512,26 +3765,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">场景</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兑现且更深</t>
+      <t xml:space="preserve">三重底三守成功</t>
     </r>
     <r>
       <rPr>
@@ -3550,7 +3784,178 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">后方向顺势转跌</t>
+      <t xml:space="preserve">后方向档位维持顺势非追结果——独立依据</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势标签</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-7.17%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">深位未变</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破位反压</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,314.66</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未收复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派组合延续</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动能衰减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">现价距三重底仅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.15%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">封深跌故押中不押大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">冻结前规则</t>
     </r>
     <r>
       <rPr>
@@ -3569,245 +3974,36 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">非追结果——独立依据</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破位结构</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">($4,310-4,334</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三重支撑带单日全数跌穿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隔夜贴</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,289</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低位横盘无反抽</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势标签</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-7.16%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连续加深</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">幅度押中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破位惯性</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日日均波幅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.99%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">但</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,265</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三重底近在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.5%+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">央行承接封深跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
+      <t xml:space="preserve">动能衰减强信号优先中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);</t>
     </r>
     <r>
       <rPr>
@@ -3826,26 +4022,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">23/20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">达标校准良好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.7pp(Brier0.2473),</t>
+      <t xml:space="preserve">24/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">达标良好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2.5pp(Brier0.2454),</t>
     </r>
     <r>
       <rPr>
@@ -3873,26 +4069,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">三条待改项待用户定夺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本判断沿用冻结前规则</t>
+      <t xml:space="preserve">三条待改项仍待用户定夺</t>
     </r>
     <r>
       <rPr>
@@ -4739,7 +4916,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6351,64 +6528,82 @@
       <c r="C25" s="9" t="n">
         <v>4289.1</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="H25" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="11" t="str">
+      <c r="I25" s="9" t="n">
+        <v>4272.2</v>
+      </c>
+      <c r="J25" s="11" t="n">
         <f aca="false">IF(OR(I25="",C25=""),"",(I25-C25)/C25)</f>
-        <v/>
+        <v>-0.00394022055909178</v>
       </c>
       <c r="K25" s="8" t="str">
         <f aca="false">IF(J25="","",IF(J25&gt;0,"涨",IF(J25&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L25" s="8" t="str">
         <f aca="false">IF(J25="","",IF(ABS(J25)&lt;=0.003,"小",IF(ABS(J25)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M25" s="8" t="str">
         <f aca="false">IF(OR(D25="",K25=""),"",IF(D25=K25,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N25" s="8" t="str">
         <f aca="false">IF(OR(E25="",L25=""),"",IF(E25=L25,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O25" s="16" t="s">
+        <v>√</v>
+      </c>
+      <c r="O25" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="P25" s="16" t="s">
+      <c r="P25" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="Q25" s="16" t="s">
+      <c r="Q25" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="R25" s="0" t="n">
+      <c r="R25" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="A26" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>4273.2</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I26" s="5"/>
       <c r="J26" s="7" t="str">
         <f aca="false">IF(OR(I26="",C26=""),"",(I26-C26)/C26)</f>
@@ -6430,9 +6625,18 @@
         <f aca="false">IF(OR(E26="",L26=""),"",IF(E26=L26,"√","×"))</f>
         <v/>
       </c>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
+      <c r="O26" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q26" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="R26" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8"/>
@@ -19209,75 +19413,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.565217391304348</v>
+        <v>0.583333333333333</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.391304347826087</v>
+        <v>0.416666666666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.565217391304348</v>
+        <v>0.583333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.391304347826087</v>
+        <v>0.416666666666667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.529411764705882</v>
+        <v>0.555555555555556</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -19286,33 +19490,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -19340,47 +19544,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19388,7 +19592,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19396,31 +19600,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19428,47 +19632,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -2358,6 +2358,19 @@
     <t xml:space="preserve">2026-09-25 06:38</t>
   </si>
   <si>
+    <t xml:space="preserve">趋势跌(20日-7.17%连续第4日深位)·60日+7.3%长期涨vs10日LBMA-2.32%短期续弱背离·FOMC鹰派落地后第7交易日·三重底$4,265-4,267上沿压缩待变(-0.15%)·耐用品订单+密歇根终值日</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2365,7 +2378,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">趋势跌</t>
+      <t xml:space="preserve">日趋势跌</t>
     </r>
     <r>
       <rPr>
@@ -2375,7 +2388,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(20</t>
+      <t xml:space="preserve">-7.17%</t>
     </r>
     <r>
       <rPr>
@@ -2384,7 +2397,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve">连续深位顺势</t>
     </r>
     <r>
       <rPr>
@@ -2394,7 +2407,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-7.17%</t>
+      <t xml:space="preserve">[</t>
     </r>
     <r>
       <rPr>
@@ -2403,7 +2416,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">连续第</t>
+      <t xml:space="preserve">已定价</t>
     </r>
     <r>
       <rPr>
@@ -2413,7 +2426,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4</t>
+      <t xml:space="preserve">]+</t>
     </r>
     <r>
       <rPr>
@@ -2422,7 +2435,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日深位</t>
+      <t xml:space="preserve">破位结构未修复</t>
     </r>
     <r>
       <rPr>
@@ -2432,7 +2445,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)·60</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -2441,7 +2454,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve">未收复</t>
     </r>
     <r>
       <rPr>
@@ -2451,7 +2464,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+7.3%</t>
+      <t xml:space="preserve">$4,300/$4,314.66</t>
     </r>
     <r>
       <rPr>
@@ -2460,7 +2473,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">长期涨</t>
+      <t xml:space="preserve">反压</t>
     </r>
     <r>
       <rPr>
@@ -2470,7 +2483,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">vs10</t>
+      <t xml:space="preserve">,</t>
     </r>
     <r>
       <rPr>
@@ -2479,7 +2492,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve">隔夜横盘</t>
     </r>
     <r>
       <rPr>
@@ -2489,7 +2502,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">LBMA-2.32%</t>
+      <t xml:space="preserve">)[</t>
     </r>
     <r>
       <rPr>
@@ -2498,7 +2511,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">短期续弱背离</t>
+      <t xml:space="preserve">部分定价</t>
     </r>
     <r>
       <rPr>
@@ -2508,7 +2521,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·FOMC</t>
+      <t xml:space="preserve">]+</t>
     </r>
     <r>
       <rPr>
@@ -2517,7 +2530,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">鹰派落地后第</t>
+      <t xml:space="preserve">鹰派延续</t>
     </r>
     <r>
       <rPr>
@@ -2527,7 +2540,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -2536,7 +2549,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">交易日</t>
+      <t xml:space="preserve">点阵图</t>
     </r>
     <r>
       <rPr>
@@ -2546,7 +2559,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">16/18</t>
     </r>
     <r>
       <rPr>
@@ -2555,6 +2568,728 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">年内再加息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+PPI/CPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">热</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元一个月高位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·10Y~4.96%[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+VIX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">四连降</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14.21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险溢价归零</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">技术指标全线偏空</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日均线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">~$4,369</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">封盖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+MACD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">负</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+RSI 36.5-44.6)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晚耐用品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">密歇根若偏热点火</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs $4,265-4,267</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三重底第四次防守</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9/14/9/18/9/24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三守成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(PBOC 22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">创纪录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">波兰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2+51t,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逢低买入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+CCI-262</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超卖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动能衰减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(-1.72%→-0.39%→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隔夜平</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投机持仓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2019</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中低位抛压衰竭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五空头回补</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押顺势压缩后向下</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,265</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">止损延伸至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,240-4,262(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">三重底</t>
     </r>
     <r>
@@ -2565,7 +3300,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">$4,265-4,267</t>
+      <t xml:space="preserve">+</t>
     </r>
     <r>
       <rPr>
@@ -2574,7 +3309,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">上沿压缩待变</t>
+      <t xml:space="preserve">央行承接封深跌不押大</t>
     </r>
     <r>
       <rPr>
@@ -2584,7 +3319,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(-0.15%)·</t>
+      <t xml:space="preserve">,$4,314.66</t>
     </r>
     <r>
       <rPr>
@@ -2593,1560 +3328,11 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">耐用品订单</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">密歇根终值日</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日趋势跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-7.17%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连续深位顺势</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破位结构未修复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未收复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,300/$4,314.66</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">反压</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隔夜横盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派延续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点阵图</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16/18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年内再加息</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+PPI/CPI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">热</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元一个月高位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·10Y~4.96%[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+VIX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">四连降</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14.21</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">避险溢价归零</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">技术指标全线偏空</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日均线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">~$4,369</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">封盖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+MACD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">负</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+RSI 36.5-44.6)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">今晚耐用品</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">密歇根若偏热点火</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] vs $4,265-4,267</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三重底第四次防守</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(9/14/9/18/9/24</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三守成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">央行承接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(PBOC 22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">创纪录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">波兰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Q2+51t,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">逢低买入</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+CCI-262</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超卖</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">动能衰减</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(-1.72%→-0.39%→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隔夜平</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投机持仓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2019</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年中低位抛压衰竭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五空头回补</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押顺势压缩后向下</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,265</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">止损延伸至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,240-4,262(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三重底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">央行承接封深跌不押大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,$4,314.66</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">为翻多确认线</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:31</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/24√√(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">实际</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.39%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三重底三守成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后方向档位维持顺势非追结果——独立依据</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势标签</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-7.17%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">深位未变</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破位反压</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,314.66</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未收复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派组合延续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">动能衰减</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">现价距三重底仅</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.15%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">封深跌故押中不押大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">冻结前规则</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">动能衰减强信号优先中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">小档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">校准</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">24/20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">达标良好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+2.5pp(Brier0.2454),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">冻结期已满</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三条待改项仍待用户定夺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本沙盒无</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">recalc.py,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">soffice</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">log.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式</t>
-    </r>
+    <t xml:space="preserve">周五06:31晨间定时执行成功(克隆仓库版);昨日9/24√√(押跌/中vs实际-0.39%跌/中,三重底三守成功)后方向档位维持顺势非追结果——独立依据=趋势标签-7.17%深位未变+破位反压$4,314.66未收复+鹰派组合延续;动能衰减+现价距三重底仅-0.15%封深跌故押中不押大(冻结前规则:动能衰减强信号优先中/小档);校准24/20达标良好+2.5pp(Brier0.2454),冻结期已满,三条待改项仍待用户定夺;本沙盒无recalc.py,已用soffice重算log.xlsx公式</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -4851,7 +4037,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4913,10 +4099,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6589,52 +5771,54 @@
       <c r="C26" s="5" t="n">
         <v>4273.2</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I26" s="5"/>
-      <c r="J26" s="7" t="str">
+      <c r="I26" s="5" t="n">
+        <v>4286.2</v>
+      </c>
+      <c r="J26" s="7" t="n">
         <f aca="false">IF(OR(I26="",C26=""),"",(I26-C26)/C26)</f>
-        <v/>
+        <v>0.00304221660582233</v>
       </c>
       <c r="K26" s="4" t="str">
         <f aca="false">IF(J26="","",IF(J26&gt;0,"涨",IF(J26&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L26" s="4" t="str">
         <f aca="false">IF(J26="","",IF(ABS(J26)&lt;=0.003,"小",IF(ABS(J26)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M26" s="4" t="str">
         <f aca="false">IF(OR(D26="",K26=""),"",IF(D26=K26,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N26" s="4" t="str">
         <f aca="false">IF(OR(E26="",L26=""),"",IF(E26=L26,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O26" s="16" t="s">
+        <v>√</v>
+      </c>
+      <c r="O26" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P26" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="Q26" s="16" t="s">
+      <c r="Q26" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="R26" s="0" t="n">
+      <c r="R26" s="1" t="n">
         <v>55</v>
       </c>
     </row>
@@ -19412,84 +18596,84 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="19" t="n">
+      <c r="B3" s="18" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="18" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
         <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="20" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.583333333333333</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.416666666666667</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="20" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.583333333333333</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.416666666666667</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="18" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.555555555555556</v>
+        <v>0.526315789473684</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="B10" s="19" t="str">
+      <c r="B10" s="18" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="22" t="s">
         <v>155</v>
       </c>
     </row>
@@ -19508,7 +18692,7 @@
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19543,87 +18727,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="26" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="25" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="26" t="s">
         <v>178</v>
       </c>
     </row>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="195">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -3333,6 +3333,1717 @@
   </si>
   <si>
     <t xml:space="preserve">周五06:31晨间定时执行成功(克隆仓库版);昨日9/24√√(押跌/中vs实际-0.39%跌/中,三重底三守成功)后方向档位维持顺势非追结果——独立依据=趋势标签-7.17%深位未变+破位反压$4,314.66未收复+鹰派组合延续;动能衰减+现价距三重底仅-0.15%封深跌故押中不押大(冻结前规则:动能衰减强信号优先中/小档);校准24/20达标良好+2.5pp(Brier0.2454),冻结期已满,三条待改项仍待用户定夺;本沙盒无recalc.py,已用soffice重算log.xlsx公式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-28 06:35</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-6.74%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连续第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日深位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2.33%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期涨动能钝化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LBMA-2.85%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期续弱背离</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派落地后第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交易日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周一跳空低开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.43%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">贴三重底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,265-4,267(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第五测</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周三窗外今窗无重大事件</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周一跳空低开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.43%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">贴三重底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,265-4,267(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第五测</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-6.74%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日深位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(LBMA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">定盘三连降至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,261.05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破名义区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破位结构未修复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">距</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,300/-0.76%·$4,314.66</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反压</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/-1.1%)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派延续</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">点阵图</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16/18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年内再加息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元一个月高位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·10Y~4.96%)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+VIX14.87</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险溢价归零</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三重底前四守成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五美盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,254→$4,286</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">买盘验证</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+PBOC 22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20.2t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">创纪录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">波兰</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Q2+51t)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逢低承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+CFTC/ETF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">持仓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2019</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中低位抛压衰竭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动能衰减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1.72%→-0.39%→+0.30%)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押顺势阴跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,265</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">止损延伸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,238-4,255(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超卖封深跌不押大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周三前波动收敛</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周末后跳空低开贴三重底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方向押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位押中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势标签</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-6.74%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">深位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破位未修复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派组合延续</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非追结果式——独立依据</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周一跳空低开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.43%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回吐周五美盘全部反弹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+LBMA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">定盘三连降至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,261.05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破三重底名义区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新变化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动能衰减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1.72%→-0.39%→+0.30%)+PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周三前收敛→押中不押大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">冻结前规则</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动能衰减优先中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">校准</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">达标良好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.2pp(Brier0.2477),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">冻结期已满</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三条待改项仍待用户定夺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本判断沿用冻结前规则</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本沙盒无</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">recalc.py,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">soffice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">log.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公式</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -4037,7 +5748,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4099,6 +5810,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5823,14 +7538,30 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
+      <c r="A27" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>4267.8</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>22</v>
+      </c>
       <c r="I27" s="9"/>
       <c r="J27" s="11" t="str">
         <f aca="false">IF(OR(I27="",C27=""),"",(I27-C27)/C27)</f>
@@ -5852,9 +7583,18 @@
         <f aca="false">IF(OR(E27="",L27=""),"",IF(E27=L27,"√","×"))</f>
         <v/>
       </c>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
+      <c r="O27" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="P27" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q27" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="R27" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
@@ -18596,99 +20336,99 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>146</v>
+      <c r="A1" s="17" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="18" t="n">
+      <c r="A3" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
         <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="18" t="n">
+      <c r="A4" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" s="20" t="n">
+      <c r="A5" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
         <v>0.56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B6" s="21" t="n">
+      <c r="A6" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
         <v>0.44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="B7" s="20" t="n">
+      <c r="A7" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.56</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="B8" s="21" t="n">
+      <c r="A8" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.44</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="18" t="n">
+      <c r="A9" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.526315789473684</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="B10" s="18" t="str">
+      <c r="A10" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
-        <v>155</v>
+      <c r="A12" s="23" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
@@ -18697,10 +20437,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -18727,88 +20467,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="23" t="s">
-        <v>160</v>
+      <c r="A1" s="24" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>162</v>
+      <c r="A3" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>164</v>
+      <c r="A4" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>166</v>
+      <c r="A5" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>168</v>
+      <c r="A6" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>170</v>
+      <c r="A7" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>171</v>
+      <c r="B8" s="26" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>172</v>
+      <c r="B9" s="26" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>174</v>
+      <c r="A10" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>176</v>
+      <c r="A11" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>178</v>
+      <c r="A12" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18816,47 +20556,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="199">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -3341,1709 +3341,25 @@
     <t xml:space="preserve">2026-09-28 06:35</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-6.74%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连续第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日深位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+2.33%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期涨动能钝化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LBMA-2.85%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期续弱背离</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·FOMC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派落地后第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">交易日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周一跳空低开</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.43%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">贴三重底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,265-4,267(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">第五测</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周三窗外今窗无重大事件</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周一跳空低开</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.43%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">贴三重底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,265-4,267(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">第五测</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日趋势跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-6.74%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日深位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(LBMA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">定盘三连降至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,261.05</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破名义区</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破位结构未修复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">距</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,300/-0.76%·$4,314.66</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">反压</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/-1.1%)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派延续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">点阵图</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">16/18</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年内再加息</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元一个月高位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·10Y~4.96%)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+VIX14.87</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">避险溢价归零</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三重底前四守成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五美盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,254→$4,286</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">买盘验证</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+PBOC 22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20.2t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">创纪录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">波兰</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Q2+51t)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">逢低承接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+CFTC/ETF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">持仓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2019</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年中低位抛压衰竭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">动能衰减</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">近</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-1.72%→-0.39%→+0.30%)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押顺势阴跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,265</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">止损延伸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,238-4,255(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">央行承接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超卖封深跌不押大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周三前波动收敛</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:31</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周末后跳空低开贴三重底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">方向押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">档位押中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势标签</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-6.74%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">深位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破位未修复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派组合延续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非追结果式——独立依据</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周一跳空低开</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.43%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回吐周五美盘全部反弹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+LBMA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">定盘三连降至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,261.05</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破三重底名义区</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">新变化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">动能衰减</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">近</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-1.72%→-0.39%→+0.30%)+PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周三前收敛→押中不押大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">冻结前规则</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">动能衰减优先中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">小档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">校准</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25/20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">达标良好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.2pp(Brier0.2477),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">冻结期已满</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三条待改项仍待用户定夺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本判断沿用冻结前规则</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本沙盒无</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">recalc.py,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">soffice</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">log.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式</t>
-    </r>
+    <t xml:space="preserve">趋势跌(20日-6.74%连续第5日深位)·60日+2.33%长期涨动能钝化vs10日LBMA-2.85%短期续弱背离·FOMC鹰派落地后第8交易日·周一跳空低开-0.43%贴三重底$4,265-4,267(第五测)·PCE周三窗外今窗无重大事件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周一跳空低开-0.43%贴三重底$4,265-4,267(第五测)[未释放]+20日趋势跌-6.74%第5日深位(LBMA定盘三连降至$4,261.05破名义区)[已定价]+破位结构未修复(距$4,300/-0.76%·$4,314.66反压/-1.1%)[部分定价]+鹰派延续(点阵图16/18年内再加息+美元一个月高位·10Y~4.96%)[已定价]+VIX14.87避险溢价归零[部分定价] vs 三重底前四守成功+周五美盘$4,254→$4,286买盘验证[未释放]+PBOC 22连月(8月+20.2t创纪录,波兰Q2+51t)逢低承接[未释放]+CFTC/ETF持仓2019年中低位抛压衰竭[未释放]+动能衰减(近3窗-1.72%→-0.39%→+0.30%)[未释放]→押顺势阴跌:破$4,265止损延伸$4,238-4,255(中档),央行承接+超卖封深跌不押大,PCE周三前波动收敛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周一06:31晨间定时执行成功(克隆仓库版);周末后跳空低开贴三重底,方向押跌+档位押中:趋势标签-6.74%深位+破位未修复+鹰派组合延续,非追结果式——独立依据=周一跳空低开-0.43%回吐周五美盘全部反弹+LBMA定盘三连降至$4,261.05破三重底名义区(新变化);动能衰减(近3窗-1.72%→-0.39%→+0.30%)+PCE周三前收敛→押中不押大(冻结前规则:动能衰减优先中/小档);校准25/20达标良好+0.2pp(Brier0.2477),冻结期已满,三条待改项仍待用户定夺,本判断沿用冻结前规则;本沙盒无recalc.py,已用soffice重算log.xlsx公式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29 06:38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">趋势跌（20日-6.74%·LBMA口径未含昨-3.31%·现货约-9.9%本轮最深）·长期涨钝化vs短期深跌背离·昨破位大阴后首日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">破位惯性+美元强+Fed年内再加息预期压顶 vs 昨-3.31%超卖+地缘避险+央行购金承接；主路径惯性阴跌中档</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -5558,12 +3874,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
-    <numFmt numFmtId="167" formatCode="General"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="168" formatCode="General"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -5813,7 +4130,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5825,7 +4142,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5833,11 +4150,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7547,64 +5864,82 @@
       <c r="C27" s="9" t="n">
         <v>4267.8</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H27" s="16" t="s">
+      <c r="H27" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="11" t="str">
+      <c r="I27" s="9" t="n">
+        <v>4126.5</v>
+      </c>
+      <c r="J27" s="11" t="n">
         <f aca="false">IF(OR(I27="",C27=""),"",(I27-C27)/C27)</f>
-        <v/>
+        <v>-0.0331083930830873</v>
       </c>
       <c r="K27" s="8" t="str">
         <f aca="false">IF(J27="","",IF(J27&gt;0,"涨",IF(J27&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L27" s="8" t="str">
         <f aca="false">IF(J27="","",IF(ABS(J27)&lt;=0.003,"小",IF(ABS(J27)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>大</v>
       </c>
       <c r="M27" s="8" t="str">
         <f aca="false">IF(OR(D27="",K27=""),"",IF(D27=K27,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N27" s="8" t="str">
         <f aca="false">IF(OR(E27="",L27=""),"",IF(E27=L27,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O27" s="16" t="s">
+        <v>×</v>
+      </c>
+      <c r="O27" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="P27" s="16" t="s">
+      <c r="P27" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="Q27" s="16" t="s">
+      <c r="Q27" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="R27" s="0" t="n">
+      <c r="R27" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="A28" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>4122.8</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="I28" s="5"/>
       <c r="J28" s="7" t="str">
         <f aca="false">IF(OR(I28="",C28=""),"",(I28-C28)/C28)</f>
@@ -7626,9 +5961,16 @@
         <f aca="false">IF(OR(E28="",L28=""),"",IF(E28=L28,"√","×"))</f>
         <v/>
       </c>
-      <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
+      <c r="O28" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="Q28" s="4"/>
+      <c r="R28" s="1" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8"/>
@@ -20337,75 +18679,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.56</v>
+        <v>0.576923076923077</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.44</v>
+        <v>0.423076923076923</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.56</v>
+        <v>0.576923076923077</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.44</v>
+        <v>0.423076923076923</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.526315789473684</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -20414,33 +18756,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -20468,47 +18810,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="24" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20516,7 +18858,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20524,31 +18866,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20556,47 +18898,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="204">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -3360,6 +3360,1822 @@
   </si>
   <si>
     <t xml:space="preserve">破位惯性+美元强+Fed年内再加息预期压顶 vs 昨-3.31%超卖+地缘避险+央行购金承接；主路径惯性阴跌中档</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30 06:35</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-9.17%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本轮最深</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·LBMA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">定盘五连降</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.1%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期横盘钝化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-2.87%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期续弱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨超卖大反弹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.41%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后首日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗内</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">锯齿交替第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗严格交替</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.41%→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今回吐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-9.17%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">深位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派组合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息概率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70%+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元一个月高位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+10Y~4.96%)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反弹供给压力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,193-4,222</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破位区下沿套牢盘密集</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏热概率高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(PPI/CPI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双热前瞻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行购金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(PBOC 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20.2t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">创纪录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,125/4,100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双支撑承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超卖修复动能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连强势买盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">投机持仓</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2019</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中低位抛压衰竭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">轧空空间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">地缘避险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美伊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关税通胀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押惯性回吐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">事件日亚欧盘收敛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双支撑封深跌故押中不押大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,139-4,168;PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏冷续反弹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">($4,193-4,222)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25%,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏热重挫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(&lt;$4,139)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">约</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周三</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);9/29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">××(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实际</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.41%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">场景树</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兑现且超上沿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后方向续押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非追结果式——独立依据</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交替规律</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗样本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势标签</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-9.17%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未变</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派组合延续</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏热概率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨反弹驱动</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">预期降温</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">属未兑现即抢跑需今晚数据验证</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位维持中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">事件日收敛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-9.17%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超卖封深跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双支撑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(-1.33%/-1.93%)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">校准</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">达标良好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.2pp(Brier0.2481),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三条待改项仍待用户定夺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本判断沿用冻结前规则</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本沙盒无</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">recalc.py,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">soffice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">log.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公式</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -4065,7 +5881,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4131,6 +5947,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5940,26 +7760,28 @@
       <c r="H28" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I28" s="5"/>
-      <c r="J28" s="7" t="str">
+      <c r="I28" s="5" t="n">
+        <v>4181</v>
+      </c>
+      <c r="J28" s="7" t="n">
         <f aca="false">IF(OR(I28="",C28=""),"",(I28-C28)/C28)</f>
-        <v/>
+        <v>0.0141166197729698</v>
       </c>
       <c r="K28" s="4" t="str">
         <f aca="false">IF(J28="","",IF(J28&gt;0,"涨",IF(J28&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L28" s="4" t="str">
         <f aca="false">IF(J28="","",IF(ABS(J28)&lt;=0.003,"小",IF(ABS(J28)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>大</v>
       </c>
       <c r="M28" s="4" t="str">
         <f aca="false">IF(OR(D28="",K28=""),"",IF(D28=K28,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N28" s="4" t="str">
         <f aca="false">IF(OR(E28="",L28=""),"",IF(E28=L28,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>153</v>
@@ -5973,14 +7795,30 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
+      <c r="A29" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>4180.5</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="I29" s="9"/>
       <c r="J29" s="11" t="str">
         <f aca="false">IF(OR(I29="",C29=""),"",(I29-C29)/C29)</f>
@@ -6002,9 +7840,18 @@
         <f aca="false">IF(OR(E29="",L29=""),"",IF(E29=L29,"√","×"))</f>
         <v/>
       </c>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
+      <c r="O29" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="P29" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q29" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="R29" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
@@ -18678,111 +20525,111 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
-        <v>155</v>
+      <c r="A1" s="18" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="19" t="n">
+      <c r="A3" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="20" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="B4" s="19" t="n">
+      <c r="A4" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="20" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="B5" s="21" t="n">
+      <c r="A5" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.576923076923077</v>
+        <v>0.555555555555556</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B6" s="22" t="n">
+      <c r="A6" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.423076923076923</v>
+        <v>0.407407407407407</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="B7" s="21" t="n">
+      <c r="A7" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.576923076923077</v>
+        <v>0.555555555555556</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B8" s="22" t="n">
+      <c r="A8" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.423076923076923</v>
+        <v>0.407407407407407</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="B9" s="19" t="n">
+      <c r="A9" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.55</v>
+        <v>0.523809523809524</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="B10" s="19" t="str">
+      <c r="A10" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="20" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
-        <v>164</v>
+      <c r="A12" s="24" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -18809,88 +20656,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>169</v>
+      <c r="A1" s="25" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>171</v>
+      <c r="A3" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>173</v>
+      <c r="A4" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>175</v>
+      <c r="A5" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>177</v>
+      <c r="A6" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>179</v>
+      <c r="A7" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>180</v>
+      <c r="B8" s="27" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>181</v>
+      <c r="B9" s="27" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>183</v>
+      <c r="A10" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>185</v>
+      <c r="A11" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>187</v>
+      <c r="A12" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18898,47 +20745,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="209">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -3368,6 +3368,21 @@
     <t xml:space="preserve">2026-09-30 06:35</t>
   </si>
   <si>
+    <t xml:space="preserve">趋势跌(20日-9.17%本轮最深·LBMA定盘五连降)·60日+0.1%长期横盘钝化vs10日-2.87%短期续弱·昨超卖大反弹+1.41%后首日·PCE今晚20:30窗内</t>
+  </si>
+  <si>
+    <t xml:space="preserve">锯齿交替第11窗(9/8起10窗严格交替,昨+1.41%→今回吐)[未释放]+趋势跌-9.17%深位[已定价]+鹰派组合(10月加息概率70%+美元一个月高位+10Y~4.96%)[已定价]+反弹供给压力$4,193-4,222为9/28破位区下沿套牢盘密集[部分定价]+PCE偏热概率高(PPI/CPI双热前瞻)[未释放] vs 央行购金22连月(PBOC 8月+20.2t创纪录)与$4,125/4,100双支撑承接[未释放]+超卖修复动能(美盘3连强势买盘)[部分定价]+投机持仓2019年中低位抛压衰竭/轧空空间[未释放]+地缘避险(美伊+关税通胀)[未释放]→押惯性回吐:PCE事件日亚欧盘收敛+双支撑封深跌故押中不押大,收$4,139-4,168;PCE偏冷续反弹($4,193-4,222)约25%,偏热重挫(&lt;$4,139)约15%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周三06:35晨间定时执行成功(克隆仓库版);9/29结算××(押跌/中vs实际+1.41%涨/大,场景树C兑现且超上沿)后方向续押跌:非追结果式——独立依据=交替规律(10窗样本)+趋势标签-9.17%未变+鹰派组合延续+PCE偏热概率,昨反弹驱动(预期降温)属未兑现即抢跑需今晚数据验证;档位维持中:PCE事件日收敛+20日-9.17%超卖封深跌+双支撑(-1.33%/-1.93%)近在;校准27/20达标良好-0.2pp(Brier0.2481),三条待改项仍待用户定夺,本判断沿用冻结前规则;本沙盒无recalc.py,已用soffice重算log.xlsx公式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01 06:40</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3404,45 +3419,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-9.17%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本轮最深</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·LBMA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">定盘五连降</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·60</t>
+      <t xml:space="preserve">-5.14%)·60</t>
     </r>
     <r>
       <rPr>
@@ -3461,16 +3438,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+0.1%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期横盘钝化</t>
+      <t xml:space="preserve">+2.24%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期钝化</t>
     </r>
     <r>
       <rPr>
@@ -3499,7 +3476,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-2.87%</t>
+      <t xml:space="preserve">-3.95%</t>
     </r>
     <r>
       <rPr>
@@ -3518,6 +3495,44 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">·PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏冷后修复第</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">·</t>
     </r>
     <r>
@@ -3527,85 +3542,876 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">昨超卖大反弹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1.41%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后首日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">今晚</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20:30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗内</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">锯齿交替第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">初请</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+ISM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晚窗内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非农明晚窗外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中国国庆休市整周</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏冷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">核心环比</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.2%&lt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">预期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+Williams</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仅再加息一次→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息概率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">47%[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,122-4,125</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">两次承接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+PBoC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗严格交替今日轮涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]vs12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">91%+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收益率顽固</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨日利好不涨美盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.8%[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中国国庆休市整周</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">];</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">主路径超卖修复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.1%~0.3%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周四</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);9/30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结算√√</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实际</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.56%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.43%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏离后美盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏冷不涨反跌回笼</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">场景</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兑现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方向转押涨非追结果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9/30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押跌√后逆向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)——</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">依据</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=PCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">偏冷钝化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交替</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
     </r>
     <r>
       <rPr>
@@ -3624,35 +4430,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(9/8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗严格交替</t>
+      <t xml:space="preserve">;LBMA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今起</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">403</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不可达</t>
     </r>
     <r>
       <rPr>
@@ -3671,463 +4477,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">昨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1.41%→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">今回吐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-9.17%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">深位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派组合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月加息概率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">70%+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元一个月高位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+10Y~4.96%)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">反弹供给压力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,193-4,222</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/28</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破位区下沿套牢盘密集</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏热概率高</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(PPI/CPI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双热前瞻</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] vs </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">央行购金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(PBOC 8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20.2t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">创纪录</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,125/4,100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双支撑承接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超卖修复动能</t>
+      <t xml:space="preserve">基线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/29-9/30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以次晨结算价续接</t>
     </r>
     <r>
       <rPr>
@@ -4146,769 +4515,64 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">美盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连强势买盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">投机持仓</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2019</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年中低位抛压衰竭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">轧空空间</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">地缘避险</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美伊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">关税通胀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押惯性回吐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">事件日亚欧盘收敛</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双支撑封深跌故押中不押大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,139-4,168;PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏冷续反弹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">($4,193-4,222)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">约</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25%,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏热重挫</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(&lt;$4,139)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">约</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15%</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周三</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:35</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);9/29</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">××(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">实际</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1.41%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">场景树</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兑现且超上沿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后方向续押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非追结果式——独立依据</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">交替规律</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗样本</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势标签</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-9.17%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未变</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派组合延续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏热概率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨反弹驱动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">预期降温</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">属未兑现即抢跑需今晚数据验证</t>
+      <t xml:space="preserve">已注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">source_note);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本沙盒无</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">recalc.py,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公式用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LibreOffice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重算</t>
     </r>
     <r>
       <rPr>
@@ -4927,120 +4591,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">档位维持中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">事件日收敛</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-9.17%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超卖封深跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双支撑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(-1.33%/-1.93%)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">近在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">校准</t>
     </r>
     <r>
@@ -5051,130 +4601,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">27/20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">达标良好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.2pp(Brier0.2481),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三条待改项仍待用户定夺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本判断沿用冻结前规则</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本沙盒无</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">recalc.py,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">soffice</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">log.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式</t>
+      <t xml:space="preserve">28/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">良好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.4pp,Brier0.2464</t>
     </r>
   </si>
   <si>
@@ -5950,7 +5396,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7804,64 +7250,82 @@
       <c r="C29" s="9" t="n">
         <v>4180.5</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="17" t="s">
+      <c r="F29" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G29" s="17" t="s">
+      <c r="G29" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H29" s="17" t="s">
+      <c r="H29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="11" t="str">
+      <c r="I29" s="9" t="n">
+        <v>4157.2</v>
+      </c>
+      <c r="J29" s="11" t="n">
         <f aca="false">IF(OR(I29="",C29=""),"",(I29-C29)/C29)</f>
-        <v/>
+        <v>-0.00557349599330228</v>
       </c>
       <c r="K29" s="8" t="str">
         <f aca="false">IF(J29="","",IF(J29&gt;0,"涨",IF(J29&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L29" s="8" t="str">
         <f aca="false">IF(J29="","",IF(ABS(J29)&lt;=0.003,"小",IF(ABS(J29)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M29" s="8" t="str">
         <f aca="false">IF(OR(D29="",K29=""),"",IF(D29=K29,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N29" s="8" t="str">
         <f aca="false">IF(OR(E29="",L29=""),"",IF(E29=L29,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O29" s="17" t="s">
+        <v>√</v>
+      </c>
+      <c r="O29" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="P29" s="17" t="s">
+      <c r="P29" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="Q29" s="17" t="s">
+      <c r="Q29" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="R29" s="0" t="n">
+      <c r="R29" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="A30" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>4157.3</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="I30" s="5"/>
       <c r="J30" s="7" t="str">
         <f aca="false">IF(OR(I30="",C30=""),"",(I30-C30)/C30)</f>
@@ -7883,9 +7347,18 @@
         <f aca="false">IF(OR(E30="",L30=""),"",IF(E30=L30,"√","×"))</f>
         <v/>
       </c>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
+      <c r="O30" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q30" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="R30" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8"/>
@@ -20526,75 +19999,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B3" s="20" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B4" s="20" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B5" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.555555555555556</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.407407407407407</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.555555555555556</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.407407407407407</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.523809523809524</v>
+        <v>0.545454545454545</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B10" s="20" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -20603,33 +20076,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -20657,47 +20130,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20705,7 +20178,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20713,31 +20186,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20745,47 +20218,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -3383,6 +3383,19 @@
     <t xml:space="preserve">2026-10-01 06:40</t>
   </si>
   <si>
+    <t xml:space="preserve">趋势跌(20日-5.14%)·60日+2.24%长期钝化vs10日-3.95%短期续弱·PCE偏冷后修复第2日·初请+ISM今晚窗内/非农明晚窗外·中国国庆休市整周</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PCE</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3390,7 +3403,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">趋势跌</t>
+      <t xml:space="preserve">偏冷</t>
     </r>
     <r>
       <rPr>
@@ -3400,7 +3413,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(20</t>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
@@ -3409,7 +3422,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve">核心环比</t>
     </r>
     <r>
       <rPr>
@@ -3419,7 +3432,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-5.14%)·60</t>
+      <t xml:space="preserve">+0.2%&lt;</t>
     </r>
     <r>
       <rPr>
@@ -3428,7 +3441,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve">预期</t>
     </r>
     <r>
       <rPr>
@@ -3438,7 +3451,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+2.24%</t>
+      <t xml:space="preserve">)+Williams</t>
     </r>
     <r>
       <rPr>
@@ -3447,7 +3460,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">长期钝化</t>
+      <t xml:space="preserve">仅再加息一次→</t>
     </r>
     <r>
       <rPr>
@@ -3457,7 +3470,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">vs10</t>
+      <t xml:space="preserve">10</t>
     </r>
     <r>
       <rPr>
@@ -3466,7 +3479,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve">月加息概率</t>
     </r>
     <r>
       <rPr>
@@ -3476,7 +3489,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-3.95%</t>
+      <t xml:space="preserve">47%[</t>
     </r>
     <r>
       <rPr>
@@ -3485,7 +3498,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">短期续弱</t>
+      <t xml:space="preserve">部分定价</t>
     </r>
     <r>
       <rPr>
@@ -3495,7 +3508,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·PCE</t>
+      <t xml:space="preserve">]+</t>
     </r>
     <r>
       <rPr>
@@ -3504,7 +3517,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">偏冷后修复第</t>
+      <t xml:space="preserve">双底</t>
     </r>
     <r>
       <rPr>
@@ -3514,7 +3527,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2</t>
+      <t xml:space="preserve">$4,122-4,125</t>
     </r>
     <r>
       <rPr>
@@ -3523,7 +3536,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日</t>
+      <t xml:space="preserve">两次承接</t>
     </r>
     <r>
       <rPr>
@@ -3533,7 +3546,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">+PBoC</t>
     </r>
     <r>
       <rPr>
@@ -3542,7 +3555,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">初请</t>
+      <t xml:space="preserve">连买</t>
     </r>
     <r>
       <rPr>
@@ -3552,7 +3565,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+ISM</t>
+      <t xml:space="preserve">22</t>
     </r>
     <r>
       <rPr>
@@ -3561,7 +3574,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">今晚窗内</t>
+      <t xml:space="preserve">个月</t>
     </r>
     <r>
       <rPr>
@@ -3571,7 +3584,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">[</t>
     </r>
     <r>
       <rPr>
@@ -3580,7 +3593,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">非农明晚窗外</t>
+      <t xml:space="preserve">已定价</t>
     </r>
     <r>
       <rPr>
@@ -3590,7 +3603,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">·</t>
+      <t xml:space="preserve">]+</t>
     </r>
     <r>
       <rPr>
@@ -3599,10 +3612,160 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗严格交替今日轮涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]vs12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">91%+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收益率顽固</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨日利好不涨美盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.8%[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">中国国庆休市整周</t>
     </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3611,7 +3774,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PCE</t>
+      <t xml:space="preserve">[</t>
     </r>
     <r>
       <rPr>
@@ -3620,7 +3783,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">偏冷</t>
+      <t xml:space="preserve">未释放</t>
     </r>
     <r>
       <rPr>
@@ -3630,7 +3793,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">];</t>
     </r>
     <r>
       <rPr>
@@ -3639,7 +3802,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">核心环比</t>
+      <t xml:space="preserve">主路径超卖修复</t>
     </r>
     <r>
       <rPr>
@@ -3649,979 +3812,11 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+0.2%&lt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">预期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+Williams</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仅再加息一次→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月加息概率</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">47%[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,122-4,125</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">两次承接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+PBoC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">近</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗严格交替今日轮涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]vs12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月加息</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">91%+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收益率顽固</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨日利好不涨美盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.8%[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中国国庆休市整周</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">];</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">主路径超卖修复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">+0.1%~0.3%</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周四</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);9/30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结算√√</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">实际</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.56%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">午后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.43%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏离后美盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏冷不涨反跌回笼</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">场景</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兑现</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">方向转押涨非追结果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(9/30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押跌√后逆向</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)——</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">依据</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=PCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">偏冷钝化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">交替</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;LBMA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">今起</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">403</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不可达</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">基线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/29-9/30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以次晨结算价续接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已注</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">source_note);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本沙盒无</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">recalc.py,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LibreOffice</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">校准</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">28/20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">良好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+1.4pp,Brier0.2464</t>
-    </r>
+    <t xml:space="preserve">周四06:40晨间定时执行(克隆仓库版);9/30结算√√(押跌/中vs实际-0.56%跌/中,午后+0.43%偏离后美盘PCE偏冷不涨反跌回笼,场景A兑现);方向转押涨非追结果(9/30押跌√后逆向)——依据=PCE偏冷钝化+双底+交替5窗;LBMA今起403不可达,基线9/29-9/30以次晨结算价续接(已注source_note);本沙盒无recalc.py,公式用LibreOffice重算;校准28/20良好+1.4pp,Brier0.2464;周六06:30补结算(10/2周五晨间任务未执行→本行漏结算):结算点10-02 06:00已无实时源,gold-api当前$4,141.80疑似冻结于10-02盘中低点区(与Investing/TE/WSJ/AP外部源全矛盾弃用),改用外部双源窗口收盘均值Investing 4,182.07+twelvedata 4,189.2→$4,185.6(两源日切≈北京06:00与预测窗口吻合,其Sep30收盘4,157.34/4,156.5与本系统10-01晨基准价$4,157.30互相验证);实际+0.68%涨/中,方向√档位×(押小档被非农反弹超上限,场景树B带)</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -5327,7 +4522,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5393,10 +4588,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7311,52 +6502,54 @@
       <c r="C30" s="5" t="n">
         <v>4157.3</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="17" t="s">
+      <c r="G30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H30" s="17" t="s">
+      <c r="H30" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="5"/>
-      <c r="J30" s="7" t="str">
+      <c r="I30" s="5" t="n">
+        <v>4185.6</v>
+      </c>
+      <c r="J30" s="7" t="n">
         <f aca="false">IF(OR(I30="",C30=""),"",(I30-C30)/C30)</f>
-        <v/>
+        <v>0.00680730281673206</v>
       </c>
       <c r="K30" s="4" t="str">
         <f aca="false">IF(J30="","",IF(J30&gt;0,"涨",IF(J30&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L30" s="4" t="str">
         <f aca="false">IF(J30="","",IF(ABS(J30)&lt;=0.003,"小",IF(ABS(J30)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M30" s="4" t="str">
         <f aca="false">IF(OR(D30="",K30=""),"",IF(D30=K30,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N30" s="4" t="str">
         <f aca="false">IF(OR(E30="",L30=""),"",IF(E30=L30,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O30" s="17" t="s">
+        <v>×</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>162</v>
       </c>
       <c r="P30" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="Q30" s="17" t="s">
+      <c r="Q30" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="R30" s="0" t="n">
+      <c r="R30" s="1" t="n">
         <v>55</v>
       </c>
     </row>
@@ -19998,84 +19191,84 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="B3" s="20" t="n">
+      <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="20" t="n">
+      <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
         <v>29</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.571428571428571</v>
+        <v>0.586206896551724</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.428571428571429</v>
+        <v>0.413793103448276</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.571428571428571</v>
+        <v>0.586206896551724</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.428571428571429</v>
+        <v>0.413793103448276</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.545454545454545</v>
+        <v>0.565217391304348</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="B10" s="20" t="str">
+      <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>174</v>
       </c>
     </row>
@@ -20094,7 +19287,7 @@
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20129,87 +19322,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="26" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="26" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="26" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="26" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="26" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>197</v>
       </c>
     </row>

--- a/log.xlsx
+++ b/log.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="214">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -3817,6 +3817,1451 @@
   </si>
   <si>
     <t xml:space="preserve">周四06:40晨间定时执行(克隆仓库版);9/30结算√√(押跌/中vs实际-0.56%跌/中,午后+0.43%偏离后美盘PCE偏冷不涨反跌回笼,场景A兑现);方向转押涨非追结果(9/30押跌√后逆向)——依据=PCE偏冷钝化+双底+交替5窗;LBMA今起403不可达,基线9/29-9/30以次晨结算价续接(已注source_note);本沙盒无recalc.py,公式用LibreOffice重算;校准28/20良好+1.4pp,Brier0.2464;周六06:30补结算(10/2周五晨间任务未执行→本行漏结算):结算点10-02 06:00已无实时源,gold-api当前$4,141.80疑似冻结于10-02盘中低点区(与Investing/TE/WSJ/AP外部源全矛盾弃用),改用外部双源窗口收盘均值Investing 4,182.07+twelvedata 4,189.2→$4,185.6(两源日切≈北京06:00与预测窗口吻合,其Sep30收盘4,157.34/4,156.5与本系统10-01晨基准价$4,157.30互相验证);实际+0.68%涨/中,方向√档位×(押小档被非农反弹超上限,场景树B带)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05 06:32</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-6.30%·9/29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起结算价续接口径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+1.34%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期钝化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-4.18%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期续弱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五非农后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.99%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大跌企稳日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·SGE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">国庆休市至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/7·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本周无重大数据</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五冲高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,227</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">遭抛回落</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.99%(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非农后收益率走高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70%/12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">88%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派组合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-6.30%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌深位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs $4,114-4,125</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底带近在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(-0.43%~-0.70%)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗涨跌严格交替周五跌今日轮涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+PBoC 22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连月购金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20.2t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">创</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023/10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以来最大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)+ETF 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月流入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$18bn[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+VIX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回落</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15.31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">恐慌消退</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押超卖修复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">主路径收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,155-4,172(+0.3%~+0.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中档下沿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">亚盘破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,130</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">防线则转跌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);10/2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五晨间任务未执行→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">行已于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周六补结算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">涨√档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">外部双源均值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,185.6),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">settle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无待结算行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10/3-10/4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周末无行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">方向续押涨非追结果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押涨√后连押</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)——</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">独立依据</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周五</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.99%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超卖宣泄落地</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">平开企稳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底带上方止跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗交替</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位改押中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">涨窗样本全为中档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(+0.88/+0.68)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">且</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押小被</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.68%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">击穿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连续两次押小失手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);LBMA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">403,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/29-10/1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结算价续接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,10/2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">漏采缺口已注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">source_note;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本沙盒无</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">recalc.py(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">按规则跳过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公式用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LibreOffice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">校准</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">达标良好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2.9pp(Brier0.2449),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三条待改项仍待用户定夺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本判断沿用冻结前规则</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -4522,7 +5967,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4588,6 +6033,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6554,14 +8003,30 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
+      <c r="A31" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>4142.8</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="I31" s="9"/>
       <c r="J31" s="11" t="str">
         <f aca="false">IF(OR(I31="",C31=""),"",(I31-C31)/C31)</f>
@@ -6583,9 +8048,18 @@
         <f aca="false">IF(OR(E31="",L31=""),"",IF(E31=L31,"√","×"))</f>
         <v/>
       </c>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8"/>
-      <c r="Q31" s="8"/>
+      <c r="O31" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="P31" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q31" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="R31" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
@@ -19191,99 +20665,99 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
-        <v>165</v>
+      <c r="A1" s="18" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="B3" s="19" t="n">
+      <c r="A3" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="20" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
         <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="19" t="n">
+      <c r="A4" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B4" s="20" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="B5" s="21" t="n">
+      <c r="A5" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
         <v>0.586206896551724</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="B6" s="22" t="n">
+      <c r="A6" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
         <v>0.413793103448276</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="B7" s="21" t="n">
+      <c r="A7" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.586206896551724</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="22" t="n">
+      <c r="A8" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.413793103448276</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="B9" s="19" t="n">
+      <c r="A9" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
         <v>0.565217391304348</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="B10" s="19" t="str">
+      <c r="A10" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="20" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
-        <v>174</v>
+      <c r="A12" s="24" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
@@ -19292,10 +20766,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -19322,88 +20796,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>179</v>
+      <c r="A1" s="25" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>181</v>
+      <c r="A3" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>183</v>
+      <c r="A4" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>185</v>
+      <c r="A5" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>187</v>
+      <c r="A6" s="26" t="s">
+        <v>191</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>189</v>
+      <c r="A7" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>190</v>
+      <c r="B8" s="27" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>191</v>
+      <c r="B9" s="27" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>193</v>
+      <c r="A10" s="26" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>195</v>
+      <c r="A11" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>197</v>
+      <c r="A12" s="26" t="s">
+        <v>201</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19411,47 +20885,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="219">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -3825,6 +3825,21 @@
     <t xml:space="preserve">2026-10-05 06:32</t>
   </si>
   <si>
+    <t xml:space="preserve">趋势跌(20日-6.30%·9/29起结算价续接口径)·60日+1.34%长期钝化vs10日-4.18%短期续弱·周五非农后-0.99%大跌企稳日·SGE国庆休市至10/7·本周无重大数据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周五冲高$4,227遭抛回落-0.99%(非农后收益率走高)[已定价]+10月加息70%/12月88%鹰派组合+20日-6.30%趋势跌深位[已定价] vs $4,114-4,125双底带近在(-0.43%~-0.70%)[未释放]+近11窗涨跌严格交替周五跌今日轮涨[未释放]+PBoC 22连月购金(8月+20.2t创2023/10以来最大)+ETF 8月流入$18bn[未释放]+VIX回落15.31恐慌消退[部分定价]→押超卖修复:主路径收$4,155-4,172(+0.3%~+0.7%中档下沿),亚盘破$4,130防线则转跌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周一06:32晨间定时执行成功(克隆仓库版);10/2周五晨间任务未执行→10/1行已于10/3周六补结算(涨√档×,外部双源均值$4,185.6),今晨settle无待结算行(10/3-10/4周末无行);方向续押涨非追结果(10/1押涨√后连押)——独立依据=周五-0.99%超卖宣泄落地+平开企稳+双底带上方止跌+11窗交替;档位改押中:涨窗样本全为中档(+0.88/+0.68)且10/1押小被+0.68%击穿(连续两次押小失手);LBMA仍403,基线9/29-10/1结算价续接,10/2漏采缺口已注source_note;本沙盒无recalc.py(按规则跳过),公式用LibreOffice重算;校准29/20达标良好+2.9pp(Brier0.2449),三条待改项仍待用户定夺,本判断沿用冻结前规则</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06 06:35</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3861,16 +3876,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-6.30%·9/29</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起结算价续接口径</t>
+      <t xml:space="preserve">-6.14%·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结算价续接口径</t>
     </r>
     <r>
       <rPr>
@@ -3899,7 +3914,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+1.34%</t>
+      <t xml:space="preserve">+1.1%</t>
     </r>
     <r>
       <rPr>
@@ -3937,7 +3952,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-4.18%</t>
+      <t xml:space="preserve">-4.69%</t>
     </r>
     <r>
       <rPr>
@@ -3965,26 +3980,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">周五非农后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.99%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">大跌企稳日</t>
+      <t xml:space="preserve">昨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.03%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">弱修复后动能收敛</t>
     </r>
     <r>
       <rPr>
@@ -4003,75 +4018,379 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">国庆休市至</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/7·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本周无重大数据</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五冲高</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,227</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">遭抛回落</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.99%(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非农后收益率走高</t>
+      <t xml:space="preserve">国庆休市最后一天</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10/7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">复市</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隔夜美数据偏强</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本周数据真空</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">隔夜美经济数据偏强强化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">higher-for-longer+FXS Fed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">情绪指数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">136.59</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹰派区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-6.14%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌深位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日均线下方技术偏空</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">昨场景</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">预期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.3%~0.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仅兑现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.03%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">该涨涨不动</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反弹动能衰竭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗交替轮跌窗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9/8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起严格交替</t>
     </r>
     <r>
       <rPr>
@@ -4090,36 +4409,112 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月加息</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">70%/12</t>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+SGE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">休市最后一天亚盘缺实物买盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs $4,114-4,125</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底带四守成功</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(9/14/9/18/9/24/10-1)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+PBoC 22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8</t>
     </r>
     <r>
       <rPr>
@@ -4138,54 +4533,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">88%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派组合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-6.30%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势跌深位</t>
+      <t xml:space="preserve">+20.2t)+ETF 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$18bn</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结构性托底</t>
     </r>
     <r>
       <rPr>
@@ -4204,44 +4580,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] vs $4,114-4,125</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双底带近在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(-0.43%~-0.70%)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">未释放</t>
     </r>
     <r>
@@ -4252,6 +4590,44 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">]+VIX 15.31</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">低位无流动性冲击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">]+</t>
     </r>
     <r>
@@ -4261,207 +4637,74 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">近</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗涨跌严格交替周五跌今日轮涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+PBoC 22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连月购金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20.2t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">创</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2023/10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以来最大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)+ETF 8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月流入</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$18bn[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+VIX</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回落</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15.31</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">恐慌消退</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
+      <t xml:space="preserve">地缘避险残余</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美伊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">也门</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
     </r>
     <r>
       <rPr>
@@ -4489,7 +4732,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">押超卖修复</t>
+      <t xml:space="preserve">押顺势回落测底</t>
     </r>
     <r>
       <rPr>
@@ -4508,26 +4751,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">主路径收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,155-4,172(+0.3%~+0.7%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中档下沿</t>
+      <t xml:space="preserve">主路径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.3%~-0.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,115-4,132(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中档</t>
     </r>
     <r>
       <rPr>
@@ -4546,56 +4808,37 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">亚盘破</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,130</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">防线则转跌</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周一</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:32</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行成功</t>
+      <t xml:space="preserve">双底承接封深跌不押大</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周二</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行</t>
     </r>
     <r>
       <rPr>
@@ -4624,54 +4867,187 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">);10/2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五晨间任务未执行→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行已于</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周六补结算</t>
+      <t xml:space="preserve">);10/5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结算√</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实际</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.03%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">午后</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.28%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">一度在轨美盘回吐归零</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后方向转押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">非追结果式</t>
     </r>
     <r>
       <rPr>
@@ -4690,121 +5066,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">涨√档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">外部双源均值</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,185.6),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">今晨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">settle</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">无待结算行</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(10/3-10/4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周末无行</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">方向续押涨非追结果</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(10/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押涨√后连押</t>
+      <t xml:space="preserve">昨方向√</t>
     </r>
     <r>
       <rPr>
@@ -4833,35 +5095,73 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周五</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.99%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超卖宣泄落地</t>
+      <t xml:space="preserve">=①</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">弱修复证伪反弹叙事</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">预期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.3~0.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仅兑现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.03%)②12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗交替轮跌③隔夜美数据偏强</t>
     </r>
     <r>
       <rPr>
@@ -4880,45 +5180,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">平开企稳</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双底带上方止跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗交替</t>
+      <t xml:space="preserve">鹰派情绪升温④顺势结构未变</t>
     </r>
     <r>
       <rPr>
@@ -4937,7 +5199,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">档位改押中</t>
+      <t xml:space="preserve">档位押中</t>
     </r>
     <r>
       <rPr>
@@ -4956,93 +5218,36 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">涨窗样本全为中档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(+0.88/+0.68)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">且</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押小被</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.68%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">击穿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连续两次押小失手</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);LBMA</t>
+      <t xml:space="preserve">整理期跌窗样本均为中档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(-0.56/-0.99)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回落测双底带目标恰落中档区间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;LBMA</t>
     </r>
     <r>
       <rPr>
@@ -5080,45 +5285,45 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9/29-10/1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结算价续接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,10/2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">漏采缺口已注</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">source_note;</t>
+      <t xml:space="preserve">9/29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起结算价续接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(10-02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">漏采注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">source_note);</t>
     </r>
     <r>
       <rPr>
@@ -5213,7 +5418,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">29/20</t>
+      <t xml:space="preserve">30/20</t>
     </r>
     <r>
       <rPr>
@@ -5232,7 +5437,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+2.9pp(Brier0.2449),</t>
+      <t xml:space="preserve">+4.3pp(Brier0.2435),</t>
     </r>
     <r>
       <rPr>
@@ -6036,7 +6241,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8012,64 +8217,82 @@
       <c r="C31" s="9" t="n">
         <v>4142.8</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F31" s="17" t="s">
+      <c r="F31" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="17" t="s">
+      <c r="G31" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H31" s="17" t="s">
+      <c r="H31" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="11" t="str">
+      <c r="I31" s="9" t="n">
+        <v>4144.2</v>
+      </c>
+      <c r="J31" s="11" t="n">
         <f aca="false">IF(OR(I31="",C31=""),"",(I31-C31)/C31)</f>
-        <v/>
+        <v>0.00033793569566468</v>
       </c>
       <c r="K31" s="8" t="str">
         <f aca="false">IF(J31="","",IF(J31&gt;0,"涨",IF(J31&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L31" s="8" t="str">
         <f aca="false">IF(J31="","",IF(ABS(J31)&lt;=0.003,"小",IF(ABS(J31)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>小</v>
       </c>
       <c r="M31" s="8" t="str">
         <f aca="false">IF(OR(D31="",K31=""),"",IF(D31=K31,"√","×"))</f>
-        <v/>
+        <v>√</v>
       </c>
       <c r="N31" s="8" t="str">
         <f aca="false">IF(OR(E31="",L31=""),"",IF(E31=L31,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O31" s="17" t="s">
+        <v>×</v>
+      </c>
+      <c r="O31" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="P31" s="17" t="s">
+      <c r="P31" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="Q31" s="17" t="s">
+      <c r="Q31" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="R31" s="0" t="n">
+      <c r="R31" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="A32" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>4144.4</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="I32" s="5"/>
       <c r="J32" s="7" t="str">
         <f aca="false">IF(OR(I32="",C32=""),"",(I32-C32)/C32)</f>
@@ -8091,9 +8314,18 @@
         <f aca="false">IF(OR(E32="",L32=""),"",IF(E32=L32,"√","×"))</f>
         <v/>
       </c>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
+      <c r="O32" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="P32" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q32" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="R32" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8"/>
@@ -20666,75 +20898,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B3" s="20" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B4" s="20" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B5" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.586206896551724</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.413793103448276</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.586206896551724</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.413793103448276</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.565217391304348</v>
+        <v>0.583333333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B10" s="20" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -20743,33 +20975,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -20797,47 +21029,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20845,7 +21077,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20853,31 +21085,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20885,47 +21117,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="224">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -3840,6 +3840,21 @@
     <t xml:space="preserve">2026-10-06 06:35</t>
   </si>
   <si>
+    <t xml:space="preserve">趋势跌(20日-6.14%·结算价续接口径)·60日+1.1%长期钝化vs10日-4.69%短期续弱·昨+0.03%弱修复后动能收敛·SGE国庆休市最后一天(10/7复市)·隔夜美数据偏强·本周数据真空</t>
+  </si>
+  <si>
+    <t xml:space="preserve">隔夜美经济数据偏强强化higher-for-longer+FXS Fed情绪指数136.59鹰派区[已定价]+20日-6.14%趋势跌深位·日线100日均线下方技术偏空[已定价]+昨场景A预期+0.3%~0.7%仅兑现+0.03%该涨涨不动·反弹动能衰竭[未释放]+12窗交替轮跌窗(9/8起严格交替)[未释放]+SGE休市最后一天亚盘缺实物买盘[未释放] vs $4,114-4,125双底带四守成功(9/14/9/18/9/24/10-1)[未释放]+PBoC 22连月(8月+20.2t)+ETF 8月$18bn结构性托底[未释放]+VIX 15.31低位无流动性冲击[部分定价]+地缘避险残余(美伊/关税/也门)[部分定价]→押顺势回落测底:主路径-0.3%~-0.7%收$4,115-4,132(中档),双底承接封深跌不押大</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周二06:35晨间定时执行(克隆仓库版);10/5结算√×(押涨/中vs实际+0.03%涨/小,午后+0.28%一度在轨美盘回吐归零)后方向转押跌:非追结果式(昨方向√)——独立依据=①弱修复证伪反弹叙事(预期+0.3~0.7%仅兑现+0.03%)②12窗交替轮跌③隔夜美数据偏强+鹰派情绪升温④顺势结构未变;档位押中:整理期跌窗样本均为中档(-0.56/-0.99)+回落测双底带目标恰落中档区间;LBMA仍403,基线9/29起结算价续接(10-02漏采注source_note);本沙盒无recalc.py(按规则跳过),公式用LibreOffice重算;校准30/20达标良好+4.3pp(Brier0.2435),三条待改项仍待用户定夺,本判断沿用冻结前规则</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07 06:35</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3876,7 +3891,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-6.14%·</t>
+      <t xml:space="preserve">-5.35%·</t>
     </r>
     <r>
       <rPr>
@@ -3914,16 +3929,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+1.1%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期钝化</t>
+      <t xml:space="preserve">+3.15%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期温和多</t>
     </r>
     <r>
       <rPr>
@@ -3952,16 +3967,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-4.69%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期续弱</t>
+      <t xml:space="preserve">-3.63%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期修复中</t>
     </r>
     <r>
       <rPr>
@@ -3990,16 +4005,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+0.03%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">弱修复后动能收敛</t>
+      <t xml:space="preserve">+0.55%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">二连涨修复</t>
     </r>
     <r>
       <rPr>
@@ -4018,45 +4033,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">国庆休市最后一天</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(10/7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">复市</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隔夜美数据偏强</t>
+      <t xml:space="preserve">国庆后复市首日</t>
     </r>
     <r>
       <rPr>
@@ -4083,48 +4060,20 @@
       <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隔夜美经济数据偏强强化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">higher-for-longer+FXS Fed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">情绪指数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">136.59</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派区</t>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SGE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">复市首日实物买盘回归</t>
     </r>
     <r>
       <rPr>
@@ -4143,6 +4092,177 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息预期降温</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(reduced rate hike expectations)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">二连涨修复动能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美盘主动买盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">亚盘贴地美盘拉升</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底带</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,114-4,125</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">五守</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">已定价</t>
     </r>
     <r>
@@ -4153,7 +4273,83 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">]+20</t>
+      <t xml:space="preserve">]+PBoC 22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20.2t)+ETF 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$18bn[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs 20</t>
     </r>
     <r>
       <rPr>
@@ -4172,35 +4368,54 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-6.14%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势跌深位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日线</t>
+      <t xml:space="preserve">-5.35%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌深位未反转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元逼近</t>
     </r>
     <r>
       <rPr>
@@ -4219,7 +4434,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">日均线下方技术偏空</t>
+      <t xml:space="preserve">关口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收益率高企</t>
     </r>
     <r>
       <rPr>
@@ -4257,83 +4491,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">昨场景</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">预期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.3%~0.7%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仅兑现</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.03%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">该涨涨不动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">反弹动能衰竭</t>
+      <t xml:space="preserve">上方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,186/4,227</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阻力密集获利了结</t>
     </r>
     <r>
       <rPr>
@@ -4362,35 +4539,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">]+12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗交替轮跌窗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(9/8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起严格交替</t>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险溢价消退</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Kitco:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">难持续</t>
     </r>
     <r>
       <rPr>
@@ -4409,215 +4586,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+SGE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">休市最后一天亚盘缺实物买盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] vs $4,114-4,125</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双底带四守成功</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(9/14/9/18/9/24/10-1)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+PBoC 22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20.2t)+ETF 8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$18bn</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结构性托底</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+VIX 15.31</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低位无流动性冲击</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">部分定价</t>
     </r>
     <r>
@@ -4628,16 +4596,141 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">地缘避险残余</t>
+      <t xml:space="preserve">]→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押复市修复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">主路径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.3%~+0.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,178-4,195(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">失守</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,153</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">转回落</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周三</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行</t>
     </r>
     <r>
       <rPr>
@@ -4656,7 +4749,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">美伊</t>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);10/6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×√(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押跌</t>
     </r>
     <r>
       <rPr>
@@ -4675,7 +4806,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">关税</t>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实际</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.55%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">涨</t>
     </r>
     <r>
       <rPr>
@@ -4694,45 +4863,102 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">也门</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押顺势回落测底</t>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">亚盘贴地横盘美盘空头回补</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+SGE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">复市抢跑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">场景</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兑现</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">后方向转押涨</t>
     </r>
     <r>
       <rPr>
@@ -4751,45 +4977,311 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">主路径</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.3%~-0.7%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,115-4,132(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中档</t>
+      <t xml:space="preserve">非追结果——独立依据</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=①SGE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今日复市实物买盘落地②</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息预期降温③二连涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美盘主动买盘④昨报场景</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已预警</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">档位押中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">整理期涨窗样本全为中档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(+0.88/+0.68/+0.55)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">主路径目标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,178-4,195</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">恰落中档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;LBMA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">403,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9/29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起结算价续接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晨续接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10/6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,10-02</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">漏采注</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">source_note);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本沙盒无</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">recalc.py(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">按规则跳过</t>
     </r>
     <r>
       <rPr>
@@ -4808,379 +5300,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">双底承接封深跌不押大</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周二</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:35</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);10/5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结算√</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">实际</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.03%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">小</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">午后</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.28%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">一度在轨美盘回吐归零</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后方向转押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非追结果式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨方向√</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)——</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">独立依据</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=①</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">弱修复证伪反弹叙事</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">预期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.3~0.7%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仅兑现</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.03%)②12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">窗交替轮跌③隔夜美数据偏强</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹰派情绪升温④顺势结构未变</t>
+      <t xml:space="preserve">公式用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LibreOffice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重算</t>
     </r>
     <r>
       <rPr>
@@ -5199,215 +5338,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">档位押中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">整理期跌窗样本均为中档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(-0.56/-0.99)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回落测双底带目标恰落中档区间</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;LBMA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仍</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">403,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">基线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/29</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起结算价续接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(10-02</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">漏采注</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">source_note);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本沙盒无</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">recalc.py(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">按规则跳过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LibreOffice</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">校准</t>
     </r>
     <r>
@@ -5418,7 +5348,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">30/20</t>
+      <t xml:space="preserve">31/20</t>
     </r>
     <r>
       <rPr>
@@ -5437,7 +5367,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+4.3pp(Brier0.2435),</t>
+      <t xml:space="preserve">+2.4pp(Brier0.2454),</t>
     </r>
     <r>
       <rPr>
@@ -6241,7 +6171,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8278,64 +8208,82 @@
       <c r="C32" s="5" t="n">
         <v>4144.4</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="17" t="s">
+      <c r="G32" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H32" s="17" t="s">
+      <c r="H32" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I32" s="5"/>
-      <c r="J32" s="7" t="str">
+      <c r="I32" s="5" t="n">
+        <v>4167.2</v>
+      </c>
+      <c r="J32" s="7" t="n">
         <f aca="false">IF(OR(I32="",C32=""),"",(I32-C32)/C32)</f>
-        <v/>
+        <v>0.00550139947881483</v>
       </c>
       <c r="K32" s="4" t="str">
         <f aca="false">IF(J32="","",IF(J32&gt;0,"涨",IF(J32&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L32" s="4" t="str">
         <f aca="false">IF(J32="","",IF(ABS(J32)&lt;=0.003,"小",IF(ABS(J32)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M32" s="4" t="str">
         <f aca="false">IF(OR(D32="",K32=""),"",IF(D32=K32,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N32" s="4" t="str">
         <f aca="false">IF(OR(E32="",L32=""),"",IF(E32=L32,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O32" s="17" t="s">
+        <v>√</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="P32" s="17" t="s">
+      <c r="P32" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="Q32" s="17" t="s">
+      <c r="Q32" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="R32" s="0" t="n">
+      <c r="R32" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
+      <c r="A33" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>4165.9</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="I33" s="9"/>
       <c r="J33" s="11" t="str">
         <f aca="false">IF(OR(I33="",C33=""),"",(I33-C33)/C33)</f>
@@ -8357,9 +8305,18 @@
         <f aca="false">IF(OR(E33="",L33=""),"",IF(E33=L33,"√","×"))</f>
         <v/>
       </c>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8"/>
-      <c r="Q33" s="8"/>
+      <c r="O33" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q33" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="R33" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
@@ -20898,57 +20855,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B3" s="20" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B4" s="20" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B5" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.6</v>
+        <v>0.580645161290323</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.4</v>
+        <v>0.419354838709677</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.6</v>
+        <v>0.566666666666667</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
@@ -20957,16 +20914,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.583333333333333</v>
+        <v>0.56</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B10" s="20" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -20975,33 +20932,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -21029,47 +20986,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21077,7 +21034,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21085,31 +21042,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21117,47 +21074,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="229">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -3855,6 +3855,666 @@
     <t xml:space="preserve">2026-10-07 06:35</t>
   </si>
   <si>
+    <t xml:space="preserve">趋势跌(20日-5.35%·结算价续接口径)·60日+3.15%长期温和多vs10日-3.63%短期修复中·昨+0.55%二连涨修复·SGE国庆后复市首日·本周数据真空</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SGE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">复市首日实物买盘回归</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息预期降温</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(reduced rate hike expectations)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">二连涨修复动能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美盘主动买盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">亚盘贴地美盘拉升</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底带</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,114-4,125</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">五守</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+PBoC 22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+20.2t)+ETF 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$18bn[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">] vs 20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-5.35%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌深位未反转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元逼近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关口</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收益率高企</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,186/4,227</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阻力密集获利了结</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险溢价消退</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Kitco:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">难持续</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押复市修复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">主路径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.3%~+0.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,178-4,195(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">),</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">失守</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">$4,153</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">转回落</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">周三06:35晨间定时执行(克隆仓库版);10/6结算×√(押跌/中vs实际+0.55%涨/中,亚盘贴地横盘美盘空头回补+SGE复市抢跑,场景C兑现)后方向转押涨:非追结果——独立依据=①SGE今日复市实物买盘落地②10月加息预期降温③二连涨+美盘主动买盘④昨报场景C已预警;档位押中:整理期涨窗样本全为中档(+0.88/+0.68/+0.55)+主路径目标$4,178-4,195恰落中档;LBMA仍403,基线9/29起结算价续接(今晨续接10/6收盘,10-02漏采注source_note);本沙盒无recalc.py(按规则跳过),公式用LibreOffice重算;校准31/20达标良好+2.4pp(Brier0.2454),三条待改项仍待用户定夺,本判断沿用冻结前规则</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08 06:35</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3891,7 +4551,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-5.35%·</t>
+      <t xml:space="preserve">-6.64%·</t>
     </r>
     <r>
       <rPr>
@@ -3929,16 +4589,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+3.15%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期温和多</t>
+      <t xml:space="preserve">+0.77%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">长期钝化</t>
     </r>
     <r>
       <rPr>
@@ -3967,16 +4627,16 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">-3.63%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期修复中</t>
+      <t xml:space="preserve">-3.74%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期走低</t>
     </r>
     <r>
       <rPr>
@@ -4005,35 +4665,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">+0.55%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">二连涨修复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·SGE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">国庆后复市首日</t>
+      <t xml:space="preserve">-1.42%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4144</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底带</t>
     </r>
     <r>
       <rPr>
@@ -4052,28 +4712,75 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">本周数据真空</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SGE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">复市首日实物买盘回归</t>
+      <t xml:space="preserve">锯齿交替跌腿增强</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">数据真空周</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息预期回摆</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破位续跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:4144</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底带失守</t>
     </r>
     <r>
       <rPr>
@@ -4092,6 +4799,82 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+higher-for-longer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回摆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">油价反弹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">强工业数据推升通胀预期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">未释放</t>
     </r>
     <r>
@@ -4102,26 +4885,216 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">]+10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月加息预期降温</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(reduced rate hike expectations)[</t>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元近月高位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">锯齿结构走弱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回调递增</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-0.57→-0.99→-1.45·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">反弹递减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+0.88→+0.68→+0.55)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+SGE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">复市买盘证伪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">；对冲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:RSI41</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">超卖修复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收益率自数十年高位回落</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
     </r>
     <r>
       <rPr>
@@ -4149,7 +5122,408 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">二连涨修复动能</t>
+      <t xml:space="preserve">央行购金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(WGC+PBoC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">连买</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">关税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">伊朗避险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周四</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);10/7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">结算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">××(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押涨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">vs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实际</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1.42%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">跌破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4144</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">双底带</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨报场景</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">兑现超预期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本窗押跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">破位</t>
     </r>
     <r>
       <rPr>
@@ -4168,273 +5542,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">美盘主动买盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">亚盘贴地美盘拉升</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双底带</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,114-4,125</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">五守</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+PBoC 22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+20.2t)+ETF 8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$18bn[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] vs 20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-5.35%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势跌深位未反转</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元逼近</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">关口</t>
+      <t xml:space="preserve">下降阶梯</t>
     </r>
     <r>
       <rPr>
@@ -4453,417 +5561,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">收益率高企</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上方</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,186/4,227</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">阻力密集获利了结</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">避险溢价消退</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Kitco:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">难持续</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押复市修复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">主路径</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.3%~+0.7%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,178-4,195(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">失守</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,153</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">转回落</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周三</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:35</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);10/6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×√(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">实际</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.55%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
+      <t xml:space="preserve">加息预期回摆</t>
     </r>
     <r>
       <rPr>
@@ -4882,520 +5580,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">亚盘贴地横盘美盘空头回补</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+SGE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">复市抢跑</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">场景</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兑现</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">后方向转押涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">非追结果——独立依据</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">=①SGE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">今日复市实物买盘落地②</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月加息预期降温③二连涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美盘主动买盘④昨报场景</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已预警</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">档位押中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">整理期涨窗样本全为中档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(+0.88/+0.68/+0.55)+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">主路径目标</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">$4,178-4,195</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">恰落中档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;LBMA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">仍</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">403,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">基线</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9/29</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起结算价续接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">今晨续接</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10/6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收盘</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,10-02</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">漏采注</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">source_note);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本沙盒无</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">recalc.py(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">按规则跳过</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">公式用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LibreOffice</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">校准</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">31/20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">达标良好</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+2.4pp(Brier0.2454),</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三条待改项仍待用户定夺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本判断沿用冻结前规则</t>
+      <t xml:space="preserve">独立依据链非追结果式修正</t>
     </r>
   </si>
   <si>
@@ -6171,7 +6356,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8269,64 +8454,82 @@
       <c r="C33" s="9" t="n">
         <v>4165.9</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="F33" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="G33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="17" t="s">
+      <c r="H33" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="11" t="str">
+      <c r="I33" s="9" t="n">
+        <v>4106.8</v>
+      </c>
+      <c r="J33" s="11" t="n">
         <f aca="false">IF(OR(I33="",C33=""),"",(I33-C33)/C33)</f>
-        <v/>
+        <v>-0.0141866103363017</v>
       </c>
       <c r="K33" s="8" t="str">
         <f aca="false">IF(J33="","",IF(J33&gt;0,"涨",IF(J33&lt;0,"跌","平")))</f>
-        <v/>
+        <v>跌</v>
       </c>
       <c r="L33" s="8" t="str">
         <f aca="false">IF(J33="","",IF(ABS(J33)&lt;=0.003,"小",IF(ABS(J33)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>大</v>
       </c>
       <c r="M33" s="8" t="str">
         <f aca="false">IF(OR(D33="",K33=""),"",IF(D33=K33,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N33" s="8" t="str">
         <f aca="false">IF(OR(E33="",L33=""),"",IF(E33=L33,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O33" s="17" t="s">
+        <v>×</v>
+      </c>
+      <c r="O33" s="10" t="s">
         <v>177</v>
       </c>
       <c r="P33" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="Q33" s="17" t="s">
+      <c r="Q33" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="R33" s="0" t="n">
+      <c r="R33" s="1" t="n">
         <v>55</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="A34" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>4107.1</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="I34" s="5"/>
       <c r="J34" s="7" t="str">
         <f aca="false">IF(OR(I34="",C34=""),"",(I34-C34)/C34)</f>
@@ -8348,9 +8551,18 @@
         <f aca="false">IF(OR(E34="",L34=""),"",IF(E34=L34,"√","×"))</f>
         <v/>
       </c>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
+      <c r="O34" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="P34" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q34" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="R34" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8"/>
@@ -20855,57 +21067,57 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B3" s="20" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B4" s="20" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B5" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.580645161290323</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.419354838709677</v>
+        <v>0.40625</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B7" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.566666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="19" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
@@ -20914,16 +21126,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="19" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.56</v>
+        <v>0.538461538461538</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B10" s="20" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
@@ -20932,33 +21144,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="24" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -20986,47 +21198,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="26" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="26" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21034,7 +21246,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21042,31 +21254,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21074,47 +21286,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/log.xlsx
+++ b/log.xlsx
@@ -4515,1073 +4515,13 @@
     <t xml:space="preserve">2026-10-08 06:35</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">趋势跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-6.64%·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结算价续接口径</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)·60</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.77%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">长期钝化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-3.74%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">短期走低</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">昨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-1.42%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4144</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双底带</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">锯齿交替跌腿增强</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">数据真空周</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月加息预期回摆</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破位续跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:4144</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双底带失守</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部分定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+higher-for-longer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回摆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">油价反弹</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">强工业数据推升通胀预期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">美元近月高位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">锯齿结构走弱</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回调递增</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-0.57→-0.99→-1.45·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">反弹递减</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+0.88→+0.68→+0.55)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+SGE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">复市买盘证伪</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">已定价</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；对冲</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:RSI41</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">超卖修复</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">收益率自数十年高位回落</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">央行购金</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(WGC+PBoC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">连买</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">关税</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">伊朗避险</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">未释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">周四</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">06:35</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨间定时执行</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">克隆仓库版</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);10/7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">结算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">××(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">押涨</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">实际</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-1.42%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">大</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">跌破</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4144</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">双底带</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">晨报场景</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">兑现超预期</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">本窗押跌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">破位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">下降阶梯</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加息预期回摆</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">独立依据链非追结果式修正</t>
-    </r>
+    <t xml:space="preserve">趋势跌(20日-6.64%·结算价续接口径)·60日+0.77%长期钝化vs10日-3.74%短期走低·昨-1.42%破4144双底带·锯齿交替跌腿增强·数据真空周·10月加息预期回摆</t>
+  </si>
+  <si>
+    <t xml:space="preserve">破位续跌:4144双底带失守[部分定价]+higher-for-longer回摆(油价反弹+强工业数据推升通胀预期)[未释放]+美元近月高位[已定价]+锯齿结构走弱(回调递增-0.57→-0.99→-1.45·反弹递减+0.88→+0.68→+0.55)[已定价]+SGE复市买盘证伪[已定价]；对冲:RSI41超卖修复+收益率自数十年高位回落[未释放]+央行购金(WGC+PBoC连买22月)[未释放]+关税/伊朗避险[未释放]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">周四06:35晨间定时执行(克隆仓库版);10/7结算××(押涨/中vs实际-1.42%跌/大,跌破4144双底带,晨报场景C兑现超预期);本窗押跌:破位+下降阶梯+加息预期回摆,独立依据链非追结果式修正;周六06:30补结算(10/9周五晨间任务未执行→本行漏结算):结算点10-09 06:00已无实时源,取外部双源纽约尾盘均值新浪4,132.62+Kitco4,132.50→$4,132.6(两源时刻≈北京10-09 04:30-05:09,COMEX收盘后低流动性时段与结算点偏差极小;Kitco次日10-09 04:21ET报4,199.80 up$67.30反推10-08收盘4,132.50互证;10-09亚欧盘续涨至~4,200与本系统周六实时4,195.6衔接吻合);本沙盒无recalc.py,公式用LibreOffice重算</t>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -6287,7 +5227,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6353,10 +5293,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8515,52 +7451,54 @@
       <c r="C34" s="5" t="n">
         <v>4107.1</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D34" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="17" t="s">
+      <c r="G34" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H34" s="17" t="s">
+      <c r="H34" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I34" s="5"/>
-      <c r="J34" s="7" t="str">
+      <c r="I34" s="5" t="n">
+        <v>4132.6</v>
+      </c>
+      <c r="J34" s="7" t="n">
         <f aca="false">IF(OR(I34="",C34=""),"",(I34-C34)/C34)</f>
-        <v/>
+        <v>0.00620876043923937</v>
       </c>
       <c r="K34" s="4" t="str">
         <f aca="false">IF(J34="","",IF(J34&gt;0,"涨",IF(J34&lt;0,"跌","平")))</f>
-        <v/>
+        <v>涨</v>
       </c>
       <c r="L34" s="4" t="str">
         <f aca="false">IF(J34="","",IF(ABS(J34)&lt;=0.003,"小",IF(ABS(J34)&lt;=0.01,"中","大")))</f>
-        <v/>
+        <v>中</v>
       </c>
       <c r="M34" s="4" t="str">
         <f aca="false">IF(OR(D34="",K34=""),"",IF(D34=K34,"√","×"))</f>
-        <v/>
+        <v>×</v>
       </c>
       <c r="N34" s="4" t="str">
         <f aca="false">IF(OR(E34="",L34=""),"",IF(E34=L34,"√","×"))</f>
-        <v/>
-      </c>
-      <c r="O34" s="17" t="s">
+        <v>√</v>
+      </c>
+      <c r="O34" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="P34" s="17" t="s">
+      <c r="P34" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="Q34" s="17" t="s">
+      <c r="Q34" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="R34" s="0" t="n">
+      <c r="R34" s="1" t="n">
         <v>55</v>
       </c>
     </row>
@@ -21066,84 +20004,84 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="20" t="n">
+      <c r="B3" s="19" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="B4" s="20" t="n">
+      <c r="B4" s="19" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
         <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="21" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
-        <v>0.5625</v>
+        <v>0.545454545454545</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
-        <v>0.40625</v>
+        <v>0.424242424242424</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="21" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.533333333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
-        <v>0.4</v>
+        <v>0.433333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="19" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.538461538461538</v>
+        <v>0.518518518518518</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B10" s="20" t="str">
+      <c r="B10" s="19" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>194</v>
       </c>
     </row>
@@ -21162,7 +20100,7 @@
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21197,87 +20135,87 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="26" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="26" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="25" t="s">
         <v>208</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="26" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="26" t="s">
+      <c r="A9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="26" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="26" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>217</v>
       </c>
     </row>

--- a/log.xlsx
+++ b/log.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="预测日志" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="统计" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="说明" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="预测日志" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="统计" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="说明" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="234">
   <si>
     <t xml:space="preserve">目标日期</t>
   </si>
@@ -4522,6 +4522,768 @@
   </si>
   <si>
     <t xml:space="preserve">周四06:35晨间定时执行(克隆仓库版);10/7结算××(押涨/中vs实际-1.42%跌/大,跌破4144双底带,晨报场景C兑现超预期);本窗押跌:破位+下降阶梯+加息预期回摆,独立依据链非追结果式修正;周六06:30补结算(10/9周五晨间任务未执行→本行漏结算):结算点10-09 06:00已无实时源,取外部双源纽约尾盘均值新浪4,132.62+Kitco4,132.50→$4,132.6(两源时刻≈北京10-09 04:30-05:09,COMEX收盘后低流动性时段与结算点偏差极小;Kitco次日10-09 04:21ET报4,199.80 up$67.30反推10-08收盘4,132.50互证;10-09亚欧盘续涨至~4,200与本系统周六实时4,195.6衔接吻合);本沙盒无recalc.py,公式用LibreOffice重算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-22 06:37</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">趋势跌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-3.68%·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">续接含新闻近似价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)·60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2.11% vs 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-1.03%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">短期收敛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周横盘</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4,130-4,182·4,150</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">两攻不破</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·FOMC(10/28)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前加息预期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FOMC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月加息预期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70%(FedWatch)+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">美元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">收益率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&gt;5%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高位压制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">已定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+4,150</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">两攻不破高点递减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部分定价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">]+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避险溢价退潮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">];</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">下方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4,100-4,130</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">支撑带</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">央行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月连购托底</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">窗振幅收敛至≈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">押小档</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周四</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">06:37</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间定时执行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">克隆仓库版</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">);10-09~10-21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">晨间任务未执行日志空窗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">今晨恢复</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;10-21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无待结算行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">校准</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">33/20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">良好</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(-1.1pp,Brier0.2489);LBMA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">仍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">403</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基线手工续接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">含新闻近似价</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">见</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">source_note);soffice</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重算公式</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">黄金预测评分统计</t>
@@ -5227,7 +5989,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5293,6 +6055,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5412,8 +6178,183 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1f497d"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="eeece1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4f81bd"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="c0504d"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9bbb59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064a2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4bacc6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="f79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ff"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -7046,7 +7987,7 @@
       </c>
       <c r="J27" s="11" t="n">
         <f aca="false">IF(OR(I27="",C27=""),"",(I27-C27)/C27)</f>
-        <v>-0.0331083930830873</v>
+        <v>-0.0331083930830874</v>
       </c>
       <c r="K27" s="8" t="str">
         <f aca="false">IF(J27="","",IF(J27&gt;0,"涨",IF(J27&lt;0,"跌","平")))</f>
@@ -7410,7 +8351,7 @@
       </c>
       <c r="J33" s="11" t="n">
         <f aca="false">IF(OR(I33="",C33=""),"",(I33-C33)/C33)</f>
-        <v>-0.0141866103363017</v>
+        <v>-0.0141866103363018</v>
       </c>
       <c r="K33" s="8" t="str">
         <f aca="false">IF(J33="","",IF(J33&gt;0,"涨",IF(J33&lt;0,"跌","平")))</f>
@@ -7503,14 +8444,30 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
+      <c r="A35" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>4136.7</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="I35" s="9"/>
       <c r="J35" s="11" t="str">
         <f aca="false">IF(OR(I35="",C35=""),"",(I35-C35)/C35)</f>
@@ -7532,9 +8489,18 @@
         <f aca="false">IF(OR(E35="",L35=""),"",IF(E35=L35,"√","×"))</f>
         <v/>
       </c>
-      <c r="O35" s="8"/>
-      <c r="P35" s="8"/>
-      <c r="Q35" s="8"/>
+      <c r="O35" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="P35" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q35" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="R35" s="0" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
@@ -19992,7 +20958,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -20004,99 +20970,99 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="17" t="s">
-        <v>185</v>
+      <c r="A1" s="18" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="19" t="n">
+      <c r="A3" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="20" t="n">
         <f aca="false">COUNTIF(预测日志!M2:M1000,"√")+COUNTIF(预测日志!M2:M1000,"×")</f>
         <v>33</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="B4" s="19" t="n">
+      <c r="A4" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="B4" s="20" t="n">
         <f aca="false">COUNTA(预测日志!A2:A1000)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="B5" s="21" t="n">
+      <c r="A5" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="22" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!M2:M1000,"√")/B3,"-")</f>
         <v>0.545454545454545</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="B6" s="22" t="n">
+      <c r="A6" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <f aca="false">IFERROR(COUNTIF(预测日志!N2:N1000,"√")/(COUNTIF(预测日志!N2:N1000,"√")+COUNTIF(预测日志!N2:N1000,"×")),"-")</f>
         <v>0.424242424242424</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" s="21" t="n">
+      <c r="A7" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="B7" s="22" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$M$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="22" t="n">
+      <c r="A8" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" s="23" t="n">
         <f aca="true">IFERROR(COUNTIF(OFFSET(预测日志!$N$1,B3-MIN(30,B3)+1,0,MIN(30,B3),1),"√")/MIN(30,B3),"-")</f>
         <v>0.433333333333333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="19" t="n">
+      <c r="A9" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="20" t="n">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"趋势*",预测日志!M2:M1000,"×")),"-")</f>
-        <v>0.518518518518518</v>
+        <v>0.518518518518519</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="19" t="str">
+      <c r="A10" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10" s="20" t="str">
         <f aca="false">IFERROR(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")/(COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!O2:O1000,"震荡",预测日志!M2:M1000,"×")),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
-        <v>194</v>
+      <c r="A12" s="24" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B13" s="1" t="n">
         <f aca="false">COUNT(预测日志!R2:R1000)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B14" s="1" t="n">
         <f aca="false">COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"√")+COUNTIFS(预测日志!R2:R1000,"&gt;0",预测日志!M2:M1000,"×")</f>
@@ -20105,10 +21071,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -20123,7 +21089,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -20135,88 +21101,88 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>199</v>
+      <c r="A1" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>201</v>
+      <c r="A3" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>203</v>
+      <c r="A4" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>205</v>
+      <c r="A5" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>207</v>
+      <c r="A6" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>209</v>
+      <c r="A7" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>210</v>
+      <c r="B8" s="27" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="26" t="s">
-        <v>211</v>
+      <c r="B9" s="27" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>213</v>
+      <c r="A10" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>215</v>
+      <c r="A11" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>217</v>
+      <c r="A12" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20224,47 +21190,47 @@
         <v>17</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
